--- a/01_要件定義/03_WBS.xlsx
+++ b/01_要件定義/03_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\01_要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3336B56-09D8-459D-AD55-09073BF7CEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF9524F-94E1-4493-8F25-90760543D450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1844,35 +1844,191 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1936,162 +2092,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2655,94 +2655,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="187" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="138" t="s">
+      <c r="C1" s="190" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="139"/>
-      <c r="E1" s="144" t="s">
+      <c r="D1" s="191"/>
+      <c r="E1" s="196" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="147" t="s">
+      <c r="F1" s="199" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="129">
+      <c r="G1" s="181">
         <v>45536</v>
       </c>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="130"/>
-      <c r="P1" s="130"/>
-      <c r="Q1" s="130"/>
-      <c r="R1" s="130"/>
-      <c r="S1" s="130"/>
-      <c r="T1" s="130"/>
-      <c r="U1" s="130"/>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
-      <c r="X1" s="130"/>
-      <c r="Y1" s="130"/>
-      <c r="Z1" s="130"/>
-      <c r="AA1" s="130"/>
-      <c r="AB1" s="130"/>
-      <c r="AC1" s="130"/>
-      <c r="AD1" s="130"/>
-      <c r="AE1" s="130"/>
-      <c r="AF1" s="130"/>
-      <c r="AG1" s="130"/>
-      <c r="AH1" s="130"/>
-      <c r="AI1" s="130"/>
-      <c r="AJ1" s="131"/>
-      <c r="AK1" s="129">
+      <c r="H1" s="182"/>
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="182"/>
+      <c r="N1" s="182"/>
+      <c r="O1" s="182"/>
+      <c r="P1" s="182"/>
+      <c r="Q1" s="182"/>
+      <c r="R1" s="182"/>
+      <c r="S1" s="182"/>
+      <c r="T1" s="182"/>
+      <c r="U1" s="182"/>
+      <c r="V1" s="182"/>
+      <c r="W1" s="182"/>
+      <c r="X1" s="182"/>
+      <c r="Y1" s="182"/>
+      <c r="Z1" s="182"/>
+      <c r="AA1" s="182"/>
+      <c r="AB1" s="182"/>
+      <c r="AC1" s="182"/>
+      <c r="AD1" s="182"/>
+      <c r="AE1" s="182"/>
+      <c r="AF1" s="182"/>
+      <c r="AG1" s="182"/>
+      <c r="AH1" s="182"/>
+      <c r="AI1" s="182"/>
+      <c r="AJ1" s="183"/>
+      <c r="AK1" s="181">
         <v>45566</v>
       </c>
-      <c r="AL1" s="130"/>
-      <c r="AM1" s="130"/>
-      <c r="AN1" s="130"/>
-      <c r="AO1" s="130"/>
-      <c r="AP1" s="130"/>
-      <c r="AQ1" s="130"/>
-      <c r="AR1" s="130"/>
-      <c r="AS1" s="130"/>
-      <c r="AT1" s="130"/>
-      <c r="AU1" s="130"/>
-      <c r="AV1" s="130"/>
-      <c r="AW1" s="130"/>
-      <c r="AX1" s="130"/>
-      <c r="AY1" s="130"/>
-      <c r="AZ1" s="130"/>
-      <c r="BA1" s="130"/>
-      <c r="BB1" s="130"/>
-      <c r="BC1" s="130"/>
-      <c r="BD1" s="130"/>
-      <c r="BE1" s="130"/>
-      <c r="BF1" s="130"/>
-      <c r="BG1" s="130"/>
-      <c r="BH1" s="130"/>
-      <c r="BI1" s="130"/>
-      <c r="BJ1" s="130"/>
-      <c r="BK1" s="130"/>
-      <c r="BL1" s="130"/>
-      <c r="BM1" s="130"/>
-      <c r="BN1" s="131"/>
+      <c r="AL1" s="182"/>
+      <c r="AM1" s="182"/>
+      <c r="AN1" s="182"/>
+      <c r="AO1" s="182"/>
+      <c r="AP1" s="182"/>
+      <c r="AQ1" s="182"/>
+      <c r="AR1" s="182"/>
+      <c r="AS1" s="182"/>
+      <c r="AT1" s="182"/>
+      <c r="AU1" s="182"/>
+      <c r="AV1" s="182"/>
+      <c r="AW1" s="182"/>
+      <c r="AX1" s="182"/>
+      <c r="AY1" s="182"/>
+      <c r="AZ1" s="182"/>
+      <c r="BA1" s="182"/>
+      <c r="BB1" s="182"/>
+      <c r="BC1" s="182"/>
+      <c r="BD1" s="182"/>
+      <c r="BE1" s="182"/>
+      <c r="BF1" s="182"/>
+      <c r="BG1" s="182"/>
+      <c r="BH1" s="182"/>
+      <c r="BI1" s="182"/>
+      <c r="BJ1" s="182"/>
+      <c r="BK1" s="182"/>
+      <c r="BL1" s="182"/>
+      <c r="BM1" s="182"/>
+      <c r="BN1" s="183"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="133"/>
-      <c r="B2" s="136"/>
-      <c r="C2" s="140"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="145"/>
-      <c r="F2" s="148"/>
+      <c r="A2" s="185"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="192"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="200"/>
       <c r="G2" s="43">
         <v>45537</v>
       </c>
@@ -2984,12 +2984,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="134"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="142"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="146"/>
-      <c r="F3" s="149"/>
+      <c r="A3" s="186"/>
+      <c r="B3" s="189"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="201"/>
       <c r="G3" s="45" t="s">
         <v>14</v>
       </c>
@@ -3172,20 +3172,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="159">
+      <c r="A4" s="174">
         <v>1</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="160" t="s">
+      <c r="C4" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="161"/>
-      <c r="E4" s="162" t="s">
+      <c r="D4" s="176"/>
+      <c r="E4" s="177" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="164" t="s">
+      <c r="F4" s="179" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="89"/>
@@ -3250,12 +3250,12 @@
       <c r="BN4" s="65"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="151"/>
+      <c r="A5" s="170"/>
       <c r="B5" s="31"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="163"/>
-      <c r="F5" s="165"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="178"/>
+      <c r="F5" s="180"/>
       <c r="G5" s="90"/>
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
@@ -3318,18 +3318,18 @@
       <c r="BN5" s="66"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="150">
+      <c r="A6" s="169">
         <v>2</v>
       </c>
       <c r="B6" s="31"/>
       <c r="C6" s="152" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="126"/>
-      <c r="E6" s="155" t="s">
+      <c r="D6" s="135"/>
+      <c r="E6" s="171" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="157" t="s">
+      <c r="F6" s="173" t="s">
         <v>40</v>
       </c>
       <c r="G6" s="47"/>
@@ -3394,12 +3394,12 @@
       <c r="BN6" s="67"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="151"/>
+      <c r="A7" s="170"/>
       <c r="B7" s="31"/>
       <c r="C7" s="153"/>
       <c r="D7" s="154"/>
-      <c r="E7" s="156"/>
-      <c r="F7" s="158"/>
+      <c r="E7" s="172"/>
+      <c r="F7" s="147"/>
       <c r="G7" s="48"/>
       <c r="H7" s="102"/>
       <c r="I7" s="58"/>
@@ -3462,20 +3462,20 @@
       <c r="BN7" s="68"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="119">
+      <c r="A8" s="121">
         <v>3</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="166" t="s">
+      <c r="C8" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="167"/>
-      <c r="E8" s="170" t="s">
+      <c r="D8" s="160"/>
+      <c r="E8" s="163" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="172" t="s">
+      <c r="F8" s="150" t="s">
         <v>41</v>
       </c>
       <c r="G8" s="35"/>
@@ -3540,12 +3540,12 @@
       <c r="BN8" s="69"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="120"/>
+      <c r="A9" s="133"/>
       <c r="B9" s="34"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="169"/>
-      <c r="E9" s="171"/>
-      <c r="F9" s="173"/>
+      <c r="C9" s="161"/>
+      <c r="D9" s="162"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="141"/>
       <c r="G9" s="49"/>
       <c r="H9" s="60"/>
       <c r="I9" s="60"/>
@@ -3608,20 +3608,20 @@
       <c r="BN9" s="70"/>
     </row>
     <row r="10" spans="1:66" ht="12" customHeight="1">
-      <c r="A10" s="119">
+      <c r="A10" s="121">
         <v>4</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="174" t="s">
+      <c r="C10" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="175"/>
-      <c r="E10" s="170" t="s">
+      <c r="D10" s="165"/>
+      <c r="E10" s="163" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="172" t="s">
+      <c r="F10" s="150" t="s">
         <v>39</v>
       </c>
       <c r="G10" s="46"/>
@@ -3686,12 +3686,12 @@
       <c r="BN10" s="66"/>
     </row>
     <row r="11" spans="1:66" ht="12" customHeight="1">
-      <c r="A11" s="120"/>
+      <c r="A11" s="133"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="177"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="124"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="168"/>
+      <c r="F11" s="151"/>
       <c r="G11" s="46"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
@@ -3754,18 +3754,18 @@
       <c r="BN11" s="66"/>
     </row>
     <row r="12" spans="1:66" ht="12" customHeight="1">
-      <c r="A12" s="119">
+      <c r="A12" s="121">
         <v>5</v>
       </c>
       <c r="B12" s="33"/>
       <c r="C12" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="126"/>
-      <c r="E12" s="121" t="s">
+      <c r="D12" s="135"/>
+      <c r="E12" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="123" t="s">
+      <c r="F12" s="140" t="s">
         <v>42</v>
       </c>
       <c r="G12" s="47"/>
@@ -3830,12 +3830,12 @@
       <c r="BN12" s="67"/>
     </row>
     <row r="13" spans="1:66" ht="12" customHeight="1">
-      <c r="A13" s="120"/>
+      <c r="A13" s="133"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="178"/>
-      <c r="D13" s="179"/>
-      <c r="E13" s="171"/>
-      <c r="F13" s="173"/>
+      <c r="C13" s="155"/>
+      <c r="D13" s="156"/>
+      <c r="E13" s="158"/>
+      <c r="F13" s="141"/>
       <c r="G13" s="48"/>
       <c r="H13" s="58"/>
       <c r="I13" s="58"/>
@@ -3865,8 +3865,8 @@
       <c r="AG13" s="25"/>
       <c r="AH13" s="26"/>
       <c r="AI13" s="102"/>
-      <c r="AJ13" s="200"/>
-      <c r="AK13" s="201"/>
+      <c r="AJ13" s="119"/>
+      <c r="AK13" s="120"/>
       <c r="AL13" s="118"/>
       <c r="AM13" s="24"/>
       <c r="AN13" s="25"/>
@@ -3898,20 +3898,20 @@
       <c r="BN13" s="68"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="119">
+      <c r="A14" s="121">
         <v>6</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="180" t="s">
+      <c r="C14" s="125" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="181"/>
-      <c r="E14" s="182" t="s">
+      <c r="D14" s="126"/>
+      <c r="E14" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="172" t="s">
+      <c r="F14" s="150" t="s">
         <v>43</v>
       </c>
       <c r="G14" s="35"/>
@@ -3976,12 +3976,12 @@
       <c r="BN14" s="69"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="120"/>
+      <c r="A15" s="133"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="127"/>
-      <c r="D15" s="128"/>
-      <c r="E15" s="183"/>
-      <c r="F15" s="124"/>
+      <c r="C15" s="136"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="151"/>
       <c r="G15" s="48"/>
       <c r="H15" s="58"/>
       <c r="I15" s="58"/>
@@ -4012,12 +4012,12 @@
       <c r="AH15" s="26"/>
       <c r="AI15" s="24"/>
       <c r="AJ15" s="68"/>
-      <c r="AK15" s="201"/>
-      <c r="AL15" s="24"/>
-      <c r="AM15" s="24"/>
+      <c r="AK15" s="120"/>
+      <c r="AL15" s="102"/>
+      <c r="AM15" s="102"/>
       <c r="AN15" s="25"/>
       <c r="AO15" s="26"/>
-      <c r="AP15" s="24"/>
+      <c r="AP15" s="102"/>
       <c r="AQ15" s="24"/>
       <c r="AR15" s="24"/>
       <c r="AS15" s="24"/>
@@ -4044,18 +4044,18 @@
       <c r="BN15" s="68"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="119">
+      <c r="A16" s="121">
         <v>7</v>
       </c>
       <c r="B16" s="33"/>
       <c r="C16" s="152" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="126"/>
-      <c r="E16" s="184" t="s">
+      <c r="D16" s="135"/>
+      <c r="E16" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="123" t="s">
+      <c r="F16" s="140" t="s">
         <v>43</v>
       </c>
       <c r="G16" s="47"/>
@@ -4120,12 +4120,12 @@
       <c r="BN16" s="67"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="120"/>
+      <c r="A17" s="133"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="127"/>
-      <c r="D17" s="128"/>
-      <c r="E17" s="183"/>
-      <c r="F17" s="124"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="151"/>
       <c r="G17" s="48"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -4188,18 +4188,18 @@
       <c r="BN17" s="68"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="119">
+      <c r="A18" s="121">
         <v>8</v>
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="152" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="126"/>
-      <c r="E18" s="184" t="s">
+      <c r="D18" s="135"/>
+      <c r="E18" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="123" t="s">
+      <c r="F18" s="140" t="s">
         <v>43</v>
       </c>
       <c r="G18" s="48"/>
@@ -4264,12 +4264,12 @@
       <c r="BN18" s="71"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="120"/>
+      <c r="A19" s="133"/>
       <c r="B19" s="34"/>
       <c r="C19" s="153"/>
       <c r="D19" s="154"/>
-      <c r="E19" s="185"/>
-      <c r="F19" s="173"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="141"/>
       <c r="G19" s="50"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -4332,20 +4332,20 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="119">
+      <c r="A20" s="121">
         <v>9</v>
       </c>
       <c r="B20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="180" t="s">
+      <c r="C20" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="181"/>
-      <c r="E20" s="182" t="s">
+      <c r="D20" s="126"/>
+      <c r="E20" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="172"/>
+      <c r="F20" s="150"/>
       <c r="G20" s="35"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -4408,14 +4408,14 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="120"/>
+      <c r="A21" s="133"/>
       <c r="B21" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="127"/>
-      <c r="D21" s="128"/>
-      <c r="E21" s="183"/>
-      <c r="F21" s="124"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="151"/>
       <c r="G21" s="47"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -4478,18 +4478,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="119">
+      <c r="A22" s="121">
         <v>10</v>
       </c>
       <c r="B22" s="33"/>
-      <c r="C22" s="125" t="s">
+      <c r="C22" s="134" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="126"/>
-      <c r="E22" s="184" t="s">
+      <c r="D22" s="135"/>
+      <c r="E22" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="123"/>
+      <c r="F22" s="140"/>
       <c r="G22" s="47"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4552,12 +4552,12 @@
       <c r="BN22" s="74"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="120"/>
+      <c r="A23" s="133"/>
       <c r="B23" s="33"/>
-      <c r="C23" s="127"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="183"/>
-      <c r="F23" s="124"/>
+      <c r="C23" s="136"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="149"/>
+      <c r="F23" s="151"/>
       <c r="G23" s="47"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -4620,18 +4620,18 @@
       <c r="BN23" s="74"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="119">
+      <c r="A24" s="121">
         <v>11</v>
       </c>
       <c r="B24" s="33"/>
-      <c r="C24" s="125" t="s">
+      <c r="C24" s="134" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="126"/>
-      <c r="E24" s="121" t="s">
+      <c r="D24" s="135"/>
+      <c r="E24" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="123"/>
+      <c r="F24" s="140"/>
       <c r="G24" s="48"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -4694,12 +4694,12 @@
       <c r="BN24" s="71"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="120"/>
+      <c r="A25" s="133"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="127"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="122"/>
-      <c r="F25" s="124"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="168"/>
+      <c r="F25" s="151"/>
       <c r="G25" s="48"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
@@ -4762,18 +4762,18 @@
       <c r="BN25" s="71"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="119">
+      <c r="A26" s="121">
         <v>12</v>
       </c>
       <c r="B26" s="33"/>
-      <c r="C26" s="125" t="s">
+      <c r="C26" s="134" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="126"/>
-      <c r="E26" s="121" t="s">
+      <c r="D26" s="135"/>
+      <c r="E26" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="123"/>
+      <c r="F26" s="140"/>
       <c r="G26" s="48"/>
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
@@ -4836,12 +4836,12 @@
       <c r="BN26" s="71"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="120"/>
+      <c r="A27" s="133"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="127"/>
-      <c r="D27" s="128"/>
-      <c r="E27" s="122"/>
-      <c r="F27" s="124"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="168"/>
+      <c r="F27" s="151"/>
       <c r="G27" s="48"/>
       <c r="H27" s="24"/>
       <c r="I27" s="24"/>
@@ -4904,18 +4904,18 @@
       <c r="BN27" s="71"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="119">
+      <c r="A28" s="121">
         <v>13</v>
       </c>
       <c r="B28" s="33"/>
-      <c r="C28" s="125" t="s">
+      <c r="C28" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="126"/>
-      <c r="E28" s="121" t="s">
+      <c r="D28" s="135"/>
+      <c r="E28" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="123"/>
+      <c r="F28" s="140"/>
       <c r="G28" s="79"/>
       <c r="H28" s="24"/>
       <c r="I28" s="24"/>
@@ -4978,12 +4978,12 @@
       <c r="BN28" s="71"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="120"/>
+      <c r="A29" s="133"/>
       <c r="B29" s="33"/>
-      <c r="C29" s="127"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="124"/>
+      <c r="C29" s="136"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="168"/>
+      <c r="F29" s="151"/>
       <c r="G29" s="79"/>
       <c r="H29" s="24"/>
       <c r="I29" s="24"/>
@@ -5046,18 +5046,18 @@
       <c r="BN29" s="71"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="119">
+      <c r="A30" s="121">
         <v>14</v>
       </c>
       <c r="B30" s="33"/>
-      <c r="C30" s="125" t="s">
+      <c r="C30" s="134" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="126"/>
-      <c r="E30" s="121" t="s">
+      <c r="D30" s="135"/>
+      <c r="E30" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="F30" s="123"/>
+      <c r="F30" s="140"/>
       <c r="G30" s="79"/>
       <c r="H30" s="24"/>
       <c r="I30" s="24"/>
@@ -5120,12 +5120,12 @@
       <c r="BN30" s="71"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1">
-      <c r="A31" s="120"/>
+      <c r="A31" s="133"/>
       <c r="B31" s="33"/>
-      <c r="C31" s="127"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="122"/>
-      <c r="F31" s="124"/>
+      <c r="C31" s="136"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="168"/>
+      <c r="F31" s="151"/>
       <c r="G31" s="79"/>
       <c r="H31" s="24"/>
       <c r="I31" s="24"/>
@@ -5188,18 +5188,18 @@
       <c r="BN31" s="71"/>
     </row>
     <row r="32" spans="1:66" ht="12" customHeight="1">
-      <c r="A32" s="119">
+      <c r="A32" s="121">
         <v>15</v>
       </c>
       <c r="B32" s="33"/>
-      <c r="C32" s="125" t="s">
+      <c r="C32" s="134" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="126"/>
-      <c r="E32" s="184" t="s">
+      <c r="D32" s="135"/>
+      <c r="E32" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="F32" s="123"/>
+      <c r="F32" s="140"/>
       <c r="G32" s="48"/>
       <c r="H32" s="24"/>
       <c r="I32" s="24"/>
@@ -5262,12 +5262,12 @@
       <c r="BN32" s="71"/>
     </row>
     <row r="33" spans="1:66" ht="12" customHeight="1">
-      <c r="A33" s="120"/>
+      <c r="A33" s="133"/>
       <c r="B33" s="34"/>
-      <c r="C33" s="127"/>
-      <c r="D33" s="128"/>
-      <c r="E33" s="185"/>
-      <c r="F33" s="173"/>
+      <c r="C33" s="136"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="141"/>
       <c r="G33" s="50"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8"/>
@@ -5330,20 +5330,20 @@
       <c r="BN33" s="72"/>
     </row>
     <row r="34" spans="1:66" ht="12" customHeight="1">
-      <c r="A34" s="119">
+      <c r="A34" s="121">
         <v>16</v>
       </c>
       <c r="B34" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="186" t="s">
+      <c r="C34" s="142" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="187"/>
-      <c r="E34" s="190" t="s">
+      <c r="D34" s="143"/>
+      <c r="E34" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="F34" s="192"/>
+      <c r="F34" s="131"/>
       <c r="G34" s="35"/>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
@@ -5406,12 +5406,12 @@
       <c r="BN34" s="99"/>
     </row>
     <row r="35" spans="1:66" ht="12" customHeight="1">
-      <c r="A35" s="120"/>
+      <c r="A35" s="133"/>
       <c r="B35" s="31"/>
-      <c r="C35" s="188"/>
-      <c r="D35" s="189"/>
-      <c r="E35" s="191"/>
-      <c r="F35" s="158"/>
+      <c r="C35" s="144"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="146"/>
+      <c r="F35" s="147"/>
       <c r="G35" s="47"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
@@ -5474,20 +5474,20 @@
       <c r="BN35" s="94"/>
     </row>
     <row r="36" spans="1:66" ht="12" customHeight="1">
-      <c r="A36" s="119">
+      <c r="A36" s="121">
         <v>17</v>
       </c>
-      <c r="B36" s="194" t="s">
+      <c r="B36" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="180" t="s">
+      <c r="C36" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="181"/>
-      <c r="E36" s="190" t="s">
+      <c r="D36" s="126"/>
+      <c r="E36" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="F36" s="192"/>
+      <c r="F36" s="131"/>
       <c r="G36" s="35"/>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
@@ -5550,12 +5550,12 @@
       <c r="BN36" s="99"/>
     </row>
     <row r="37" spans="1:66" ht="12" customHeight="1" thickBot="1">
-      <c r="A37" s="193"/>
-      <c r="B37" s="195"/>
-      <c r="C37" s="196"/>
-      <c r="D37" s="197"/>
-      <c r="E37" s="198"/>
-      <c r="F37" s="199"/>
+      <c r="A37" s="122"/>
+      <c r="B37" s="124"/>
+      <c r="C37" s="127"/>
+      <c r="D37" s="128"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="132"/>
       <c r="G37" s="36"/>
       <c r="H37" s="11"/>
       <c r="I37" s="11"/>
@@ -5641,11 +5641,69 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="C32:D33"/>
     <mergeCell ref="E32:E33"/>
@@ -5654,69 +5712,11 @@
     <mergeCell ref="C34:D35"/>
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/01_要件定義/03_WBS.xlsx
+++ b/01_要件定義/03_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\01_要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF9524F-94E1-4493-8F25-90760543D450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65171AA7-AE69-4812-87B8-1E7720937B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="41">
   <si>
     <t>進捗</t>
     <rPh sb="0" eb="2">
@@ -322,54 +322,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ショッピング機能（決算部分）
-カート画面</t>
-    <rPh sb="9" eb="11">
-      <t>ケッサン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ショッピング機能（決算部分）
-購入画面</t>
-    <rPh sb="9" eb="11">
-      <t>ケッサン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>コウニュウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ショッピング機能（決算部分）
-会員画面</t>
-    <rPh sb="9" eb="11">
-      <t>ケッサン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ブブン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カイイン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>奈良田</t>
     <rPh sb="0" eb="3">
       <t>ナラタ</t>
@@ -521,7 +473,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="78">
+  <borders count="77">
     <border>
       <left/>
       <right/>
@@ -666,19 +618,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1496,7 +1435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1505,78 +1444,78 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1594,39 +1533,42 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="7" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="7" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1637,84 +1579,84 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="178" fontId="2" fillId="3" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="64" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="10" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1729,132 +1671,342 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="10" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="10" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="10" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="10" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="178" fontId="2" fillId="3" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="3" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="56" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="11" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1862,236 +2014,20 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2640,7 +2576,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BN41"/>
+  <dimension ref="A1:BN35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="9.6"/>
   <cols>
     <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
@@ -2655,94 +2591,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="187" t="s">
+      <c r="B1" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="190" t="s">
+      <c r="C1" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="191"/>
-      <c r="E1" s="196" t="s">
+      <c r="D1" s="140"/>
+      <c r="E1" s="145" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="199" t="s">
+      <c r="F1" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="181">
+      <c r="G1" s="130">
         <v>45536</v>
       </c>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
-      <c r="M1" s="182"/>
-      <c r="N1" s="182"/>
-      <c r="O1" s="182"/>
-      <c r="P1" s="182"/>
-      <c r="Q1" s="182"/>
-      <c r="R1" s="182"/>
-      <c r="S1" s="182"/>
-      <c r="T1" s="182"/>
-      <c r="U1" s="182"/>
-      <c r="V1" s="182"/>
-      <c r="W1" s="182"/>
-      <c r="X1" s="182"/>
-      <c r="Y1" s="182"/>
-      <c r="Z1" s="182"/>
-      <c r="AA1" s="182"/>
-      <c r="AB1" s="182"/>
-      <c r="AC1" s="182"/>
-      <c r="AD1" s="182"/>
-      <c r="AE1" s="182"/>
-      <c r="AF1" s="182"/>
-      <c r="AG1" s="182"/>
-      <c r="AH1" s="182"/>
-      <c r="AI1" s="182"/>
-      <c r="AJ1" s="183"/>
-      <c r="AK1" s="181">
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="131"/>
+      <c r="M1" s="131"/>
+      <c r="N1" s="131"/>
+      <c r="O1" s="131"/>
+      <c r="P1" s="131"/>
+      <c r="Q1" s="131"/>
+      <c r="R1" s="131"/>
+      <c r="S1" s="131"/>
+      <c r="T1" s="131"/>
+      <c r="U1" s="131"/>
+      <c r="V1" s="131"/>
+      <c r="W1" s="131"/>
+      <c r="X1" s="131"/>
+      <c r="Y1" s="131"/>
+      <c r="Z1" s="131"/>
+      <c r="AA1" s="131"/>
+      <c r="AB1" s="131"/>
+      <c r="AC1" s="131"/>
+      <c r="AD1" s="131"/>
+      <c r="AE1" s="131"/>
+      <c r="AF1" s="131"/>
+      <c r="AG1" s="131"/>
+      <c r="AH1" s="131"/>
+      <c r="AI1" s="131"/>
+      <c r="AJ1" s="132"/>
+      <c r="AK1" s="130">
         <v>45566</v>
       </c>
-      <c r="AL1" s="182"/>
-      <c r="AM1" s="182"/>
-      <c r="AN1" s="182"/>
-      <c r="AO1" s="182"/>
-      <c r="AP1" s="182"/>
-      <c r="AQ1" s="182"/>
-      <c r="AR1" s="182"/>
-      <c r="AS1" s="182"/>
-      <c r="AT1" s="182"/>
-      <c r="AU1" s="182"/>
-      <c r="AV1" s="182"/>
-      <c r="AW1" s="182"/>
-      <c r="AX1" s="182"/>
-      <c r="AY1" s="182"/>
-      <c r="AZ1" s="182"/>
-      <c r="BA1" s="182"/>
-      <c r="BB1" s="182"/>
-      <c r="BC1" s="182"/>
-      <c r="BD1" s="182"/>
-      <c r="BE1" s="182"/>
-      <c r="BF1" s="182"/>
-      <c r="BG1" s="182"/>
-      <c r="BH1" s="182"/>
-      <c r="BI1" s="182"/>
-      <c r="BJ1" s="182"/>
-      <c r="BK1" s="182"/>
-      <c r="BL1" s="182"/>
-      <c r="BM1" s="182"/>
-      <c r="BN1" s="183"/>
+      <c r="AL1" s="131"/>
+      <c r="AM1" s="131"/>
+      <c r="AN1" s="131"/>
+      <c r="AO1" s="131"/>
+      <c r="AP1" s="131"/>
+      <c r="AQ1" s="131"/>
+      <c r="AR1" s="131"/>
+      <c r="AS1" s="131"/>
+      <c r="AT1" s="131"/>
+      <c r="AU1" s="131"/>
+      <c r="AV1" s="131"/>
+      <c r="AW1" s="131"/>
+      <c r="AX1" s="131"/>
+      <c r="AY1" s="131"/>
+      <c r="AZ1" s="131"/>
+      <c r="BA1" s="131"/>
+      <c r="BB1" s="131"/>
+      <c r="BC1" s="131"/>
+      <c r="BD1" s="131"/>
+      <c r="BE1" s="131"/>
+      <c r="BF1" s="131"/>
+      <c r="BG1" s="131"/>
+      <c r="BH1" s="131"/>
+      <c r="BI1" s="131"/>
+      <c r="BJ1" s="131"/>
+      <c r="BK1" s="131"/>
+      <c r="BL1" s="131"/>
+      <c r="BM1" s="131"/>
+      <c r="BN1" s="132"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="185"/>
-      <c r="B2" s="188"/>
-      <c r="C2" s="192"/>
-      <c r="D2" s="193"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="200"/>
+      <c r="A2" s="134"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="149"/>
       <c r="G2" s="43">
         <v>45537</v>
       </c>
@@ -2984,12 +2920,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="186"/>
-      <c r="B3" s="189"/>
-      <c r="C3" s="194"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="198"/>
-      <c r="F3" s="201"/>
+      <c r="A3" s="135"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="143"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="150"/>
       <c r="G3" s="45" t="s">
         <v>14</v>
       </c>
@@ -3172,30 +3108,30 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="174">
+      <c r="A4" s="160">
         <v>1</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="175" t="s">
+      <c r="C4" s="161" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="176"/>
-      <c r="E4" s="177" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="179" t="s">
-        <v>40</v>
+      <c r="D4" s="162"/>
+      <c r="E4" s="163" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="165" t="s">
+        <v>37</v>
       </c>
       <c r="G4" s="89"/>
-      <c r="H4" s="103"/>
+      <c r="H4" s="102"/>
       <c r="I4" s="55"/>
       <c r="J4" s="55"/>
       <c r="K4" s="55"/>
       <c r="L4" s="12"/>
       <c r="M4" s="18"/>
-      <c r="N4" s="105"/>
+      <c r="N4" s="104"/>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
@@ -3250,12 +3186,12 @@
       <c r="BN4" s="65"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="170"/>
+      <c r="A5" s="152"/>
       <c r="B5" s="31"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="180"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="164"/>
+      <c r="F5" s="166"/>
       <c r="G5" s="90"/>
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
@@ -3263,7 +3199,7 @@
       <c r="K5" s="56"/>
       <c r="L5" s="16"/>
       <c r="M5" s="22"/>
-      <c r="N5" s="111"/>
+      <c r="N5" s="110"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -3318,19 +3254,19 @@
       <c r="BN5" s="66"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="169">
+      <c r="A6" s="151">
         <v>2</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="152" t="s">
+      <c r="C6" s="153" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="127"/>
+      <c r="E6" s="156" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="158" t="s">
         <v>37</v>
-      </c>
-      <c r="D6" s="135"/>
-      <c r="E6" s="171" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="173" t="s">
-        <v>40</v>
       </c>
       <c r="G6" s="47"/>
       <c r="H6" s="29"/>
@@ -3339,7 +3275,7 @@
       <c r="K6" s="57"/>
       <c r="L6" s="13"/>
       <c r="M6" s="19"/>
-      <c r="N6" s="106"/>
+      <c r="N6" s="105"/>
       <c r="O6" s="57"/>
       <c r="P6" s="57"/>
       <c r="Q6" s="57"/>
@@ -3394,20 +3330,20 @@
       <c r="BN6" s="67"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="170"/>
+      <c r="A7" s="152"/>
       <c r="B7" s="31"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="147"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="155"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="159"/>
       <c r="G7" s="48"/>
-      <c r="H7" s="102"/>
+      <c r="H7" s="101"/>
       <c r="I7" s="58"/>
       <c r="J7" s="58"/>
       <c r="K7" s="58"/>
       <c r="L7" s="25"/>
       <c r="M7" s="26"/>
-      <c r="N7" s="112"/>
+      <c r="N7" s="111"/>
       <c r="O7" s="58"/>
       <c r="P7" s="58"/>
       <c r="Q7" s="58"/>
@@ -3462,21 +3398,21 @@
       <c r="BN7" s="68"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="121">
+      <c r="A8" s="120">
         <v>3</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="159" t="s">
+      <c r="C8" s="167" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="160"/>
-      <c r="E8" s="163" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="150" t="s">
-        <v>41</v>
+      <c r="D8" s="168"/>
+      <c r="E8" s="171" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="173" t="s">
+        <v>38</v>
       </c>
       <c r="G8" s="35"/>
       <c r="H8" s="59"/>
@@ -3493,7 +3429,7 @@
       <c r="S8" s="15"/>
       <c r="T8" s="21"/>
       <c r="U8" s="21"/>
-      <c r="V8" s="107"/>
+      <c r="V8" s="106"/>
       <c r="W8" s="6"/>
       <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
@@ -3540,12 +3476,12 @@
       <c r="BN8" s="69"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="133"/>
+      <c r="A9" s="121"/>
       <c r="B9" s="34"/>
-      <c r="C9" s="161"/>
-      <c r="D9" s="162"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="141"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="172"/>
+      <c r="F9" s="174"/>
       <c r="G9" s="49"/>
       <c r="H9" s="60"/>
       <c r="I9" s="60"/>
@@ -3553,11 +3489,11 @@
       <c r="K9" s="60"/>
       <c r="L9" s="41"/>
       <c r="M9" s="42"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="113"/>
-      <c r="P9" s="113"/>
-      <c r="Q9" s="113"/>
-      <c r="R9" s="113"/>
+      <c r="N9" s="101"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112"/>
+      <c r="Q9" s="112"/>
+      <c r="R9" s="112"/>
       <c r="S9" s="41"/>
       <c r="T9" s="42"/>
       <c r="U9" s="42"/>
@@ -3608,21 +3544,21 @@
       <c r="BN9" s="70"/>
     </row>
     <row r="10" spans="1:66" ht="12" customHeight="1">
-      <c r="A10" s="121">
+      <c r="A10" s="120">
         <v>4</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="164" t="s">
+      <c r="C10" s="175" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="165"/>
-      <c r="E10" s="163" t="s">
+      <c r="D10" s="176"/>
+      <c r="E10" s="171" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="173" t="s">
         <v>36</v>
-      </c>
-      <c r="F10" s="150" t="s">
-        <v>39</v>
       </c>
       <c r="G10" s="46"/>
       <c r="H10" s="56"/>
@@ -3635,24 +3571,24 @@
       <c r="O10" s="56"/>
       <c r="P10" s="56"/>
       <c r="Q10" s="38"/>
-      <c r="R10" s="104"/>
+      <c r="R10" s="103"/>
       <c r="S10" s="16"/>
       <c r="T10" s="22"/>
       <c r="U10" s="22"/>
-      <c r="V10" s="104"/>
+      <c r="V10" s="103"/>
       <c r="W10" s="9"/>
       <c r="X10" s="9"/>
       <c r="Y10" s="9"/>
       <c r="Z10" s="16"/>
       <c r="AA10" s="22"/>
       <c r="AB10" s="22"/>
-      <c r="AC10" s="109"/>
+      <c r="AC10" s="108"/>
       <c r="AD10" s="9"/>
       <c r="AE10" s="9"/>
       <c r="AF10" s="9"/>
       <c r="AG10" s="16"/>
       <c r="AH10" s="22"/>
-      <c r="AI10" s="109"/>
+      <c r="AI10" s="108"/>
       <c r="AJ10" s="66"/>
       <c r="AK10" s="77"/>
       <c r="AL10" s="9"/>
@@ -3686,12 +3622,12 @@
       <c r="BN10" s="66"/>
     </row>
     <row r="11" spans="1:66" ht="12" customHeight="1">
-      <c r="A11" s="133"/>
+      <c r="A11" s="121"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="166"/>
-      <c r="D11" s="167"/>
-      <c r="E11" s="168"/>
-      <c r="F11" s="151"/>
+      <c r="C11" s="177"/>
+      <c r="D11" s="178"/>
+      <c r="E11" s="123"/>
+      <c r="F11" s="125"/>
       <c r="G11" s="46"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
@@ -3700,24 +3636,24 @@
       <c r="L11" s="16"/>
       <c r="M11" s="22"/>
       <c r="N11" s="56"/>
-      <c r="O11" s="111"/>
-      <c r="P11" s="111"/>
-      <c r="Q11" s="111"/>
-      <c r="R11" s="111"/>
+      <c r="O11" s="110"/>
+      <c r="P11" s="110"/>
+      <c r="Q11" s="110"/>
+      <c r="R11" s="110"/>
       <c r="S11" s="16"/>
       <c r="T11" s="22"/>
       <c r="U11" s="22"/>
-      <c r="V11" s="111"/>
-      <c r="W11" s="111"/>
-      <c r="X11" s="111"/>
-      <c r="Y11" s="111"/>
+      <c r="V11" s="110"/>
+      <c r="W11" s="110"/>
+      <c r="X11" s="110"/>
+      <c r="Y11" s="110"/>
       <c r="Z11" s="16"/>
       <c r="AA11" s="22"/>
       <c r="AB11" s="22"/>
-      <c r="AC11" s="111"/>
-      <c r="AD11" s="111"/>
-      <c r="AE11" s="111"/>
-      <c r="AF11" s="111"/>
+      <c r="AC11" s="110"/>
+      <c r="AD11" s="110"/>
+      <c r="AE11" s="110"/>
+      <c r="AF11" s="110"/>
       <c r="AG11" s="16"/>
       <c r="AH11" s="22"/>
       <c r="AI11" s="9"/>
@@ -3754,19 +3690,19 @@
       <c r="BN11" s="66"/>
     </row>
     <row r="12" spans="1:66" ht="12" customHeight="1">
-      <c r="A12" s="121">
+      <c r="A12" s="120">
         <v>5</v>
       </c>
       <c r="B12" s="33"/>
-      <c r="C12" s="152" t="s">
+      <c r="C12" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="135"/>
-      <c r="E12" s="157" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="140" t="s">
-        <v>42</v>
+      <c r="D12" s="127"/>
+      <c r="E12" s="122" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="124" t="s">
+        <v>39</v>
       </c>
       <c r="G12" s="47"/>
       <c r="H12" s="57"/>
@@ -3790,14 +3726,14 @@
       <c r="Z12" s="13"/>
       <c r="AA12" s="19"/>
       <c r="AB12" s="19"/>
-      <c r="AC12" s="106"/>
+      <c r="AC12" s="105"/>
       <c r="AD12" s="7"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="7"/>
       <c r="AG12" s="13"/>
       <c r="AH12" s="19"/>
-      <c r="AI12" s="106"/>
-      <c r="AJ12" s="115"/>
+      <c r="AI12" s="105"/>
+      <c r="AJ12" s="114"/>
       <c r="AK12" s="95"/>
       <c r="AL12" s="7"/>
       <c r="AM12" s="7"/>
@@ -3830,12 +3766,12 @@
       <c r="BN12" s="67"/>
     </row>
     <row r="13" spans="1:66" ht="12" customHeight="1">
-      <c r="A13" s="133"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="155"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="158"/>
-      <c r="F13" s="141"/>
+      <c r="C13" s="179"/>
+      <c r="D13" s="180"/>
+      <c r="E13" s="172"/>
+      <c r="F13" s="174"/>
       <c r="G13" s="48"/>
       <c r="H13" s="58"/>
       <c r="I13" s="58"/>
@@ -3851,23 +3787,23 @@
       <c r="S13" s="25"/>
       <c r="T13" s="26"/>
       <c r="U13" s="26"/>
-      <c r="V13" s="102"/>
-      <c r="W13" s="102"/>
-      <c r="X13" s="102"/>
-      <c r="Y13" s="102"/>
+      <c r="V13" s="101"/>
+      <c r="W13" s="101"/>
+      <c r="X13" s="101"/>
+      <c r="Y13" s="101"/>
       <c r="Z13" s="25"/>
       <c r="AA13" s="26"/>
       <c r="AB13" s="26"/>
-      <c r="AC13" s="102"/>
-      <c r="AD13" s="102"/>
-      <c r="AE13" s="102"/>
-      <c r="AF13" s="102"/>
+      <c r="AC13" s="101"/>
+      <c r="AD13" s="101"/>
+      <c r="AE13" s="101"/>
+      <c r="AF13" s="101"/>
       <c r="AG13" s="25"/>
       <c r="AH13" s="26"/>
-      <c r="AI13" s="102"/>
-      <c r="AJ13" s="119"/>
-      <c r="AK13" s="120"/>
-      <c r="AL13" s="118"/>
+      <c r="AI13" s="101"/>
+      <c r="AJ13" s="118"/>
+      <c r="AK13" s="119"/>
+      <c r="AL13" s="117"/>
       <c r="AM13" s="24"/>
       <c r="AN13" s="25"/>
       <c r="AO13" s="26"/>
@@ -3898,21 +3834,21 @@
       <c r="BN13" s="68"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="121">
+      <c r="A14" s="120">
         <v>6</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="125" t="s">
+      <c r="C14" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="126"/>
-      <c r="E14" s="148" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="150" t="s">
-        <v>43</v>
+      <c r="D14" s="182"/>
+      <c r="E14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="173" t="s">
+        <v>40</v>
       </c>
       <c r="G14" s="35"/>
       <c r="H14" s="59"/>
@@ -3944,12 +3880,12 @@
       <c r="AH14" s="21"/>
       <c r="AI14" s="91"/>
       <c r="AJ14" s="69"/>
-      <c r="AK14" s="116"/>
-      <c r="AL14" s="117"/>
+      <c r="AK14" s="115"/>
+      <c r="AL14" s="116"/>
       <c r="AM14" s="6"/>
       <c r="AN14" s="15"/>
       <c r="AO14" s="21"/>
-      <c r="AP14" s="107"/>
+      <c r="AP14" s="106"/>
       <c r="AQ14" s="6"/>
       <c r="AR14" s="6"/>
       <c r="AS14" s="6"/>
@@ -3957,7 +3893,7 @@
       <c r="AU14" s="15"/>
       <c r="AV14" s="21"/>
       <c r="AW14" s="21"/>
-      <c r="AX14" s="107"/>
+      <c r="AX14" s="106"/>
       <c r="AY14" s="6"/>
       <c r="AZ14" s="6"/>
       <c r="BA14" s="6"/>
@@ -3976,12 +3912,12 @@
       <c r="BN14" s="69"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="133"/>
+      <c r="A15" s="121"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="136"/>
-      <c r="D15" s="137"/>
-      <c r="E15" s="149"/>
-      <c r="F15" s="151"/>
+      <c r="C15" s="128"/>
+      <c r="D15" s="129"/>
+      <c r="E15" s="184"/>
+      <c r="F15" s="125"/>
       <c r="G15" s="48"/>
       <c r="H15" s="58"/>
       <c r="I15" s="58"/>
@@ -4012,12 +3948,12 @@
       <c r="AH15" s="26"/>
       <c r="AI15" s="24"/>
       <c r="AJ15" s="68"/>
-      <c r="AK15" s="120"/>
-      <c r="AL15" s="102"/>
-      <c r="AM15" s="102"/>
+      <c r="AK15" s="119"/>
+      <c r="AL15" s="101"/>
+      <c r="AM15" s="101"/>
       <c r="AN15" s="25"/>
       <c r="AO15" s="26"/>
-      <c r="AP15" s="102"/>
+      <c r="AP15" s="101"/>
       <c r="AQ15" s="24"/>
       <c r="AR15" s="24"/>
       <c r="AS15" s="24"/>
@@ -4044,19 +3980,19 @@
       <c r="BN15" s="68"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="121">
+      <c r="A16" s="120">
         <v>7</v>
       </c>
       <c r="B16" s="33"/>
-      <c r="C16" s="152" t="s">
+      <c r="C16" s="153" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="135"/>
-      <c r="E16" s="138" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="140" t="s">
-        <v>43</v>
+      <c r="D16" s="127"/>
+      <c r="E16" s="185" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="124" t="s">
+        <v>40</v>
       </c>
       <c r="G16" s="47"/>
       <c r="H16" s="7"/>
@@ -4093,15 +4029,15 @@
       <c r="AM16" s="39"/>
       <c r="AN16" s="13"/>
       <c r="AO16" s="19"/>
-      <c r="AP16" s="106"/>
-      <c r="AQ16" s="7"/>
-      <c r="AR16" s="7"/>
-      <c r="AS16" s="7"/>
-      <c r="AT16" s="7"/>
+      <c r="AP16" s="105"/>
+      <c r="AQ16" s="29"/>
+      <c r="AR16" s="29"/>
+      <c r="AS16" s="29"/>
+      <c r="AT16" s="29"/>
       <c r="AU16" s="13"/>
       <c r="AV16" s="19"/>
       <c r="AW16" s="19"/>
-      <c r="AX16" s="106"/>
+      <c r="AX16" s="105"/>
       <c r="AY16" s="7"/>
       <c r="AZ16" s="7"/>
       <c r="BA16" s="7"/>
@@ -4120,12 +4056,12 @@
       <c r="BN16" s="67"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="133"/>
+      <c r="A17" s="121"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="136"/>
-      <c r="D17" s="137"/>
-      <c r="E17" s="149"/>
-      <c r="F17" s="151"/>
+      <c r="C17" s="128"/>
+      <c r="D17" s="129"/>
+      <c r="E17" s="184"/>
+      <c r="F17" s="125"/>
       <c r="G17" s="48"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -4162,10 +4098,10 @@
       <c r="AN17" s="25"/>
       <c r="AO17" s="26"/>
       <c r="AP17" s="24"/>
-      <c r="AQ17" s="24"/>
-      <c r="AR17" s="24"/>
-      <c r="AS17" s="24"/>
-      <c r="AT17" s="24"/>
+      <c r="AQ17" s="101"/>
+      <c r="AR17" s="101"/>
+      <c r="AS17" s="101"/>
+      <c r="AT17" s="101"/>
       <c r="AU17" s="25"/>
       <c r="AV17" s="26"/>
       <c r="AW17" s="26"/>
@@ -4188,19 +4124,19 @@
       <c r="BN17" s="68"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="121">
+      <c r="A18" s="120">
         <v>8</v>
       </c>
       <c r="B18" s="33"/>
-      <c r="C18" s="152" t="s">
+      <c r="C18" s="153" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="135"/>
-      <c r="E18" s="138" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="140" t="s">
-        <v>43</v>
+      <c r="D18" s="127"/>
+      <c r="E18" s="185" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="124" t="s">
+        <v>40</v>
       </c>
       <c r="G18" s="48"/>
       <c r="H18" s="24"/>
@@ -4237,15 +4173,15 @@
       <c r="AM18" s="39"/>
       <c r="AN18" s="25"/>
       <c r="AO18" s="26"/>
-      <c r="AP18" s="110"/>
-      <c r="AQ18" s="93"/>
-      <c r="AR18" s="58"/>
-      <c r="AS18" s="58"/>
-      <c r="AT18" s="58"/>
+      <c r="AP18" s="109"/>
+      <c r="AQ18" s="39"/>
+      <c r="AR18" s="39"/>
+      <c r="AS18" s="39"/>
+      <c r="AT18" s="39"/>
       <c r="AU18" s="25"/>
       <c r="AV18" s="26"/>
       <c r="AW18" s="26"/>
-      <c r="AX18" s="110"/>
+      <c r="AX18" s="109"/>
       <c r="AY18" s="58"/>
       <c r="AZ18" s="58"/>
       <c r="BA18" s="58"/>
@@ -4264,12 +4200,12 @@
       <c r="BN18" s="71"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="133"/>
+      <c r="A19" s="121"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="153"/>
-      <c r="D19" s="154"/>
-      <c r="E19" s="139"/>
-      <c r="F19" s="141"/>
+      <c r="C19" s="154"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="186"/>
+      <c r="F19" s="174"/>
       <c r="G19" s="50"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -4306,10 +4242,10 @@
       <c r="AN19" s="17"/>
       <c r="AO19" s="23"/>
       <c r="AP19" s="62"/>
-      <c r="AQ19" s="62"/>
-      <c r="AR19" s="62"/>
-      <c r="AS19" s="62"/>
-      <c r="AT19" s="62"/>
+      <c r="AQ19" s="200"/>
+      <c r="AR19" s="200"/>
+      <c r="AS19" s="200"/>
+      <c r="AT19" s="200"/>
       <c r="AU19" s="17"/>
       <c r="AV19" s="23"/>
       <c r="AW19" s="23"/>
@@ -4332,20 +4268,20 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="121">
+      <c r="A20" s="120">
         <v>9</v>
       </c>
       <c r="B20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="181" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="126"/>
-      <c r="E20" s="148" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="150"/>
+      <c r="D20" s="182"/>
+      <c r="E20" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="173"/>
       <c r="G20" s="35"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -4376,13 +4312,13 @@
       <c r="AH20" s="21"/>
       <c r="AI20" s="59"/>
       <c r="AJ20" s="73"/>
-      <c r="AK20" s="114"/>
+      <c r="AK20" s="113"/>
       <c r="AL20" s="59"/>
       <c r="AM20" s="91"/>
       <c r="AN20" s="15"/>
       <c r="AO20" s="21"/>
       <c r="AP20" s="91"/>
-      <c r="AQ20" s="37"/>
+      <c r="AQ20" s="91"/>
       <c r="AR20" s="91"/>
       <c r="AS20" s="91"/>
       <c r="AT20" s="91"/>
@@ -4390,12 +4326,12 @@
       <c r="AV20" s="21"/>
       <c r="AW20" s="21"/>
       <c r="AX20" s="59"/>
-      <c r="AY20" s="59"/>
+      <c r="AY20" s="37"/>
       <c r="AZ20" s="59"/>
       <c r="BA20" s="59"/>
       <c r="BB20" s="15"/>
       <c r="BC20" s="21"/>
-      <c r="BD20" s="107"/>
+      <c r="BD20" s="106"/>
       <c r="BE20" s="59"/>
       <c r="BF20" s="59"/>
       <c r="BG20" s="59"/>
@@ -4408,14 +4344,14 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="133"/>
+      <c r="A21" s="121"/>
       <c r="B21" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="136"/>
-      <c r="D21" s="137"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="151"/>
+      <c r="C21" s="128"/>
+      <c r="D21" s="129"/>
+      <c r="E21" s="184"/>
+      <c r="F21" s="125"/>
       <c r="G21" s="47"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -4478,18 +4414,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="121">
+      <c r="A22" s="120">
         <v>10</v>
       </c>
       <c r="B22" s="33"/>
-      <c r="C22" s="134" t="s">
+      <c r="C22" s="126" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="135"/>
-      <c r="E22" s="138" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="140"/>
+      <c r="D22" s="127"/>
+      <c r="E22" s="185" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="124"/>
       <c r="G22" s="47"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4526,7 +4462,7 @@
       <c r="AN22" s="13"/>
       <c r="AO22" s="19"/>
       <c r="AP22" s="92"/>
-      <c r="AQ22" s="29"/>
+      <c r="AQ22" s="92"/>
       <c r="AR22" s="92"/>
       <c r="AS22" s="92"/>
       <c r="AT22" s="92"/>
@@ -4534,12 +4470,12 @@
       <c r="AV22" s="19"/>
       <c r="AW22" s="19"/>
       <c r="AX22" s="57"/>
-      <c r="AY22" s="57"/>
+      <c r="AY22" s="29"/>
       <c r="AZ22" s="57"/>
       <c r="BA22" s="57"/>
       <c r="BB22" s="13"/>
       <c r="BC22" s="19"/>
-      <c r="BD22" s="106"/>
+      <c r="BD22" s="105"/>
       <c r="BE22" s="57"/>
       <c r="BF22" s="57"/>
       <c r="BG22" s="57"/>
@@ -4552,12 +4488,12 @@
       <c r="BN22" s="74"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="133"/>
+      <c r="A23" s="121"/>
       <c r="B23" s="33"/>
-      <c r="C23" s="136"/>
-      <c r="D23" s="137"/>
-      <c r="E23" s="149"/>
-      <c r="F23" s="151"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="129"/>
+      <c r="E23" s="184"/>
+      <c r="F23" s="125"/>
       <c r="G23" s="47"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -4620,18 +4556,18 @@
       <c r="BN23" s="74"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="121">
+      <c r="A24" s="120">
         <v>11</v>
       </c>
       <c r="B24" s="33"/>
-      <c r="C24" s="134" t="s">
+      <c r="C24" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="135"/>
-      <c r="E24" s="157" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="140"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="122" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="124"/>
       <c r="G24" s="48"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -4669,19 +4605,19 @@
       <c r="AO24" s="26"/>
       <c r="AP24" s="93"/>
       <c r="AQ24" s="93"/>
-      <c r="AR24" s="39"/>
+      <c r="AR24" s="93"/>
       <c r="AS24" s="93"/>
       <c r="AT24" s="93"/>
       <c r="AU24" s="25"/>
       <c r="AV24" s="26"/>
       <c r="AW24" s="26"/>
       <c r="AX24" s="58"/>
-      <c r="AY24" s="58"/>
+      <c r="AY24" s="39"/>
       <c r="AZ24" s="58"/>
       <c r="BA24" s="58"/>
       <c r="BB24" s="25"/>
       <c r="BC24" s="26"/>
-      <c r="BD24" s="110"/>
+      <c r="BD24" s="109"/>
       <c r="BE24" s="58"/>
       <c r="BF24" s="58"/>
       <c r="BG24" s="58"/>
@@ -4694,12 +4630,12 @@
       <c r="BN24" s="71"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="133"/>
+      <c r="A25" s="121"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="136"/>
-      <c r="D25" s="137"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="151"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="129"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="125"/>
       <c r="G25" s="48"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
@@ -4762,18 +4698,18 @@
       <c r="BN25" s="71"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="121">
+      <c r="A26" s="120">
         <v>12</v>
       </c>
       <c r="B26" s="33"/>
-      <c r="C26" s="134" t="s">
+      <c r="C26" s="126" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="135"/>
-      <c r="E26" s="157" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="140"/>
+      <c r="D26" s="127"/>
+      <c r="E26" s="122" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="124"/>
       <c r="G26" s="48"/>
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
@@ -4812,18 +4748,18 @@
       <c r="AP26" s="93"/>
       <c r="AQ26" s="93"/>
       <c r="AR26" s="93"/>
-      <c r="AS26" s="39"/>
+      <c r="AS26" s="93"/>
       <c r="AT26" s="93"/>
       <c r="AU26" s="25"/>
       <c r="AV26" s="26"/>
       <c r="AW26" s="26"/>
       <c r="AX26" s="93"/>
-      <c r="AY26" s="93"/>
+      <c r="AY26" s="39"/>
       <c r="AZ26" s="93"/>
       <c r="BA26" s="93"/>
       <c r="BB26" s="25"/>
       <c r="BC26" s="26"/>
-      <c r="BD26" s="110"/>
+      <c r="BD26" s="109"/>
       <c r="BE26" s="58"/>
       <c r="BF26" s="58"/>
       <c r="BG26" s="58"/>
@@ -4836,12 +4772,12 @@
       <c r="BN26" s="71"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="133"/>
+      <c r="A27" s="121"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="136"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="168"/>
-      <c r="F27" s="151"/>
+      <c r="C27" s="128"/>
+      <c r="D27" s="129"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="125"/>
       <c r="G27" s="48"/>
       <c r="H27" s="24"/>
       <c r="I27" s="24"/>
@@ -4904,751 +4840,373 @@
       <c r="BN27" s="71"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="121">
+      <c r="A28" s="120">
         <v>13</v>
       </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="134" t="s">
+      <c r="B28" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="187" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="188"/>
+      <c r="E28" s="191" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="135"/>
-      <c r="E28" s="157" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="140"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="26"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="58"/>
-      <c r="R28" s="58"/>
-      <c r="S28" s="25"/>
-      <c r="T28" s="26"/>
-      <c r="U28" s="26"/>
-      <c r="V28" s="58"/>
-      <c r="W28" s="58"/>
-      <c r="X28" s="58"/>
-      <c r="Y28" s="58"/>
-      <c r="Z28" s="25"/>
-      <c r="AA28" s="26"/>
-      <c r="AB28" s="26"/>
-      <c r="AC28" s="58"/>
-      <c r="AD28" s="58"/>
-      <c r="AE28" s="58"/>
-      <c r="AF28" s="58"/>
-      <c r="AG28" s="25"/>
-      <c r="AH28" s="26"/>
-      <c r="AI28" s="58"/>
-      <c r="AJ28" s="71"/>
-      <c r="AK28" s="82"/>
-      <c r="AL28" s="58"/>
-      <c r="AM28" s="58"/>
-      <c r="AN28" s="25"/>
-      <c r="AO28" s="26"/>
-      <c r="AP28" s="58"/>
-      <c r="AQ28" s="58"/>
-      <c r="AR28" s="58"/>
-      <c r="AS28" s="93"/>
-      <c r="AT28" s="93"/>
-      <c r="AU28" s="25"/>
-      <c r="AV28" s="26"/>
-      <c r="AW28" s="26"/>
-      <c r="AX28" s="93"/>
-      <c r="AY28" s="93"/>
-      <c r="AZ28" s="93"/>
-      <c r="BA28" s="93"/>
-      <c r="BB28" s="25"/>
-      <c r="BC28" s="26"/>
-      <c r="BD28" s="110"/>
-      <c r="BE28" s="58"/>
-      <c r="BF28" s="58"/>
-      <c r="BG28" s="58"/>
-      <c r="BH28" s="58"/>
-      <c r="BI28" s="25"/>
-      <c r="BJ28" s="26"/>
-      <c r="BK28" s="58"/>
-      <c r="BL28" s="58"/>
-      <c r="BM28" s="58"/>
-      <c r="BN28" s="71"/>
+      <c r="F28" s="193"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="59"/>
+      <c r="O28" s="59"/>
+      <c r="P28" s="59"/>
+      <c r="Q28" s="59"/>
+      <c r="R28" s="59"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="21"/>
+      <c r="V28" s="59"/>
+      <c r="W28" s="59"/>
+      <c r="X28" s="59"/>
+      <c r="Y28" s="59"/>
+      <c r="Z28" s="15"/>
+      <c r="AA28" s="21"/>
+      <c r="AB28" s="21"/>
+      <c r="AC28" s="59"/>
+      <c r="AD28" s="59"/>
+      <c r="AE28" s="59"/>
+      <c r="AF28" s="59"/>
+      <c r="AG28" s="15"/>
+      <c r="AH28" s="21"/>
+      <c r="AI28" s="59"/>
+      <c r="AJ28" s="73"/>
+      <c r="AK28" s="84"/>
+      <c r="AL28" s="59"/>
+      <c r="AM28" s="59"/>
+      <c r="AN28" s="15"/>
+      <c r="AO28" s="21"/>
+      <c r="AP28" s="59"/>
+      <c r="AQ28" s="59"/>
+      <c r="AR28" s="59"/>
+      <c r="AS28" s="59"/>
+      <c r="AT28" s="59"/>
+      <c r="AU28" s="15"/>
+      <c r="AV28" s="21"/>
+      <c r="AW28" s="21"/>
+      <c r="AX28" s="59"/>
+      <c r="AY28" s="59"/>
+      <c r="AZ28" s="37"/>
+      <c r="BA28" s="37"/>
+      <c r="BB28" s="15"/>
+      <c r="BC28" s="21"/>
+      <c r="BD28" s="37"/>
+      <c r="BE28" s="37"/>
+      <c r="BF28" s="91"/>
+      <c r="BG28" s="91"/>
+      <c r="BH28" s="91"/>
+      <c r="BI28" s="15"/>
+      <c r="BJ28" s="21"/>
+      <c r="BK28" s="91"/>
+      <c r="BL28" s="91"/>
+      <c r="BM28" s="91"/>
+      <c r="BN28" s="98"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="133"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="168"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="24"/>
-      <c r="K29" s="24"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="58"/>
-      <c r="S29" s="25"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="58"/>
-      <c r="W29" s="58"/>
-      <c r="X29" s="58"/>
-      <c r="Y29" s="58"/>
-      <c r="Z29" s="25"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="58"/>
-      <c r="AD29" s="58"/>
-      <c r="AE29" s="58"/>
-      <c r="AF29" s="58"/>
-      <c r="AG29" s="25"/>
-      <c r="AH29" s="26"/>
-      <c r="AI29" s="58"/>
-      <c r="AJ29" s="71"/>
-      <c r="AK29" s="82"/>
-      <c r="AL29" s="58"/>
-      <c r="AM29" s="58"/>
-      <c r="AN29" s="25"/>
-      <c r="AO29" s="26"/>
-      <c r="AP29" s="58"/>
-      <c r="AQ29" s="58"/>
-      <c r="AR29" s="58"/>
-      <c r="AS29" s="58"/>
-      <c r="AT29" s="58"/>
-      <c r="AU29" s="25"/>
-      <c r="AV29" s="26"/>
-      <c r="AW29" s="26"/>
-      <c r="AX29" s="93"/>
-      <c r="AY29" s="93"/>
-      <c r="AZ29" s="93"/>
-      <c r="BA29" s="93"/>
-      <c r="BB29" s="25"/>
-      <c r="BC29" s="26"/>
-      <c r="BD29" s="58"/>
-      <c r="BE29" s="58"/>
-      <c r="BF29" s="58"/>
-      <c r="BG29" s="58"/>
-      <c r="BH29" s="58"/>
-      <c r="BI29" s="25"/>
-      <c r="BJ29" s="26"/>
-      <c r="BK29" s="58"/>
-      <c r="BL29" s="58"/>
-      <c r="BM29" s="58"/>
-      <c r="BN29" s="71"/>
+      <c r="A29" s="121"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="189"/>
+      <c r="D29" s="190"/>
+      <c r="E29" s="192"/>
+      <c r="F29" s="159"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="57"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="19"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="57"/>
+      <c r="W29" s="57"/>
+      <c r="X29" s="57"/>
+      <c r="Y29" s="57"/>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="19"/>
+      <c r="AB29" s="19"/>
+      <c r="AC29" s="57"/>
+      <c r="AD29" s="57"/>
+      <c r="AE29" s="57"/>
+      <c r="AF29" s="57"/>
+      <c r="AG29" s="13"/>
+      <c r="AH29" s="19"/>
+      <c r="AI29" s="57"/>
+      <c r="AJ29" s="74"/>
+      <c r="AK29" s="85"/>
+      <c r="AL29" s="57"/>
+      <c r="AM29" s="57"/>
+      <c r="AN29" s="13"/>
+      <c r="AO29" s="19"/>
+      <c r="AP29" s="57"/>
+      <c r="AQ29" s="57"/>
+      <c r="AR29" s="57"/>
+      <c r="AS29" s="57"/>
+      <c r="AT29" s="57"/>
+      <c r="AU29" s="13"/>
+      <c r="AV29" s="19"/>
+      <c r="AW29" s="19"/>
+      <c r="AX29" s="57"/>
+      <c r="AY29" s="57"/>
+      <c r="AZ29" s="57"/>
+      <c r="BA29" s="57"/>
+      <c r="BB29" s="13"/>
+      <c r="BC29" s="19"/>
+      <c r="BD29" s="57"/>
+      <c r="BE29" s="57"/>
+      <c r="BF29" s="57"/>
+      <c r="BG29" s="57"/>
+      <c r="BH29" s="57"/>
+      <c r="BI29" s="13"/>
+      <c r="BJ29" s="19"/>
+      <c r="BK29" s="92"/>
+      <c r="BL29" s="92"/>
+      <c r="BM29" s="92"/>
+      <c r="BN29" s="94"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="121">
+      <c r="A30" s="120">
         <v>14</v>
       </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="134" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="135"/>
-      <c r="E30" s="157" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="140"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="24"/>
-      <c r="J30" s="24"/>
-      <c r="K30" s="24"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="58"/>
-      <c r="O30" s="58"/>
-      <c r="P30" s="58"/>
-      <c r="Q30" s="58"/>
-      <c r="R30" s="58"/>
-      <c r="S30" s="25"/>
-      <c r="T30" s="26"/>
-      <c r="U30" s="26"/>
-      <c r="V30" s="58"/>
-      <c r="W30" s="58"/>
-      <c r="X30" s="58"/>
-      <c r="Y30" s="58"/>
-      <c r="Z30" s="25"/>
-      <c r="AA30" s="26"/>
-      <c r="AB30" s="26"/>
-      <c r="AC30" s="58"/>
-      <c r="AD30" s="58"/>
-      <c r="AE30" s="58"/>
-      <c r="AF30" s="58"/>
-      <c r="AG30" s="25"/>
-      <c r="AH30" s="26"/>
-      <c r="AI30" s="58"/>
-      <c r="AJ30" s="71"/>
-      <c r="AK30" s="82"/>
-      <c r="AL30" s="58"/>
-      <c r="AM30" s="58"/>
-      <c r="AN30" s="25"/>
-      <c r="AO30" s="26"/>
-      <c r="AP30" s="58"/>
-      <c r="AQ30" s="58"/>
-      <c r="AR30" s="58"/>
-      <c r="AS30" s="58"/>
-      <c r="AT30" s="58"/>
-      <c r="AU30" s="25"/>
-      <c r="AV30" s="26"/>
-      <c r="AW30" s="26"/>
-      <c r="AX30" s="93"/>
-      <c r="AY30" s="93"/>
-      <c r="AZ30" s="93"/>
-      <c r="BA30" s="93"/>
-      <c r="BB30" s="25"/>
-      <c r="BC30" s="26"/>
-      <c r="BD30" s="110"/>
-      <c r="BE30" s="93"/>
-      <c r="BF30" s="93"/>
-      <c r="BG30" s="93"/>
-      <c r="BH30" s="93"/>
-      <c r="BI30" s="25"/>
-      <c r="BJ30" s="26"/>
-      <c r="BK30" s="58"/>
-      <c r="BL30" s="58"/>
-      <c r="BM30" s="58"/>
-      <c r="BN30" s="71"/>
+      <c r="B30" s="194" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="181" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="182"/>
+      <c r="E30" s="191" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="193"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="15"/>
+      <c r="T30" s="21"/>
+      <c r="U30" s="21"/>
+      <c r="V30" s="59"/>
+      <c r="W30" s="59"/>
+      <c r="X30" s="59"/>
+      <c r="Y30" s="59"/>
+      <c r="Z30" s="15"/>
+      <c r="AA30" s="21"/>
+      <c r="AB30" s="21"/>
+      <c r="AC30" s="59"/>
+      <c r="AD30" s="59"/>
+      <c r="AE30" s="59"/>
+      <c r="AF30" s="59"/>
+      <c r="AG30" s="15"/>
+      <c r="AH30" s="21"/>
+      <c r="AI30" s="59"/>
+      <c r="AJ30" s="73"/>
+      <c r="AK30" s="84"/>
+      <c r="AL30" s="59"/>
+      <c r="AM30" s="59"/>
+      <c r="AN30" s="15"/>
+      <c r="AO30" s="21"/>
+      <c r="AP30" s="59"/>
+      <c r="AQ30" s="59"/>
+      <c r="AR30" s="59"/>
+      <c r="AS30" s="59"/>
+      <c r="AT30" s="59"/>
+      <c r="AU30" s="15"/>
+      <c r="AV30" s="21"/>
+      <c r="AW30" s="21"/>
+      <c r="AX30" s="59"/>
+      <c r="AY30" s="59"/>
+      <c r="AZ30" s="59"/>
+      <c r="BA30" s="59"/>
+      <c r="BB30" s="15"/>
+      <c r="BC30" s="21"/>
+      <c r="BD30" s="91"/>
+      <c r="BE30" s="91"/>
+      <c r="BF30" s="37"/>
+      <c r="BG30" s="37"/>
+      <c r="BH30" s="37"/>
+      <c r="BI30" s="15"/>
+      <c r="BJ30" s="21"/>
+      <c r="BK30" s="91"/>
+      <c r="BL30" s="91"/>
+      <c r="BM30" s="91"/>
+      <c r="BN30" s="98"/>
     </row>
-    <row r="31" spans="1:66" ht="12" customHeight="1">
-      <c r="A31" s="133"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="136"/>
-      <c r="D31" s="137"/>
-      <c r="E31" s="168"/>
-      <c r="F31" s="151"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="24"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="25"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="26"/>
-      <c r="V31" s="58"/>
-      <c r="W31" s="58"/>
-      <c r="X31" s="58"/>
-      <c r="Y31" s="58"/>
-      <c r="Z31" s="25"/>
-      <c r="AA31" s="26"/>
-      <c r="AB31" s="26"/>
-      <c r="AC31" s="58"/>
-      <c r="AD31" s="58"/>
-      <c r="AE31" s="58"/>
-      <c r="AF31" s="58"/>
-      <c r="AG31" s="25"/>
-      <c r="AH31" s="26"/>
-      <c r="AI31" s="58"/>
-      <c r="AJ31" s="71"/>
-      <c r="AK31" s="82"/>
-      <c r="AL31" s="58"/>
-      <c r="AM31" s="58"/>
-      <c r="AN31" s="25"/>
-      <c r="AO31" s="26"/>
-      <c r="AP31" s="58"/>
-      <c r="AQ31" s="58"/>
-      <c r="AR31" s="58"/>
-      <c r="AS31" s="58"/>
-      <c r="AT31" s="58"/>
-      <c r="AU31" s="25"/>
-      <c r="AV31" s="26"/>
-      <c r="AW31" s="26"/>
-      <c r="AX31" s="93"/>
-      <c r="AY31" s="93"/>
-      <c r="AZ31" s="93"/>
-      <c r="BA31" s="93"/>
-      <c r="BB31" s="25"/>
-      <c r="BC31" s="26"/>
-      <c r="BD31" s="93"/>
-      <c r="BE31" s="93"/>
-      <c r="BF31" s="93"/>
-      <c r="BG31" s="93"/>
-      <c r="BH31" s="93"/>
-      <c r="BI31" s="25"/>
-      <c r="BJ31" s="26"/>
-      <c r="BK31" s="58"/>
-      <c r="BL31" s="58"/>
-      <c r="BM31" s="58"/>
-      <c r="BN31" s="71"/>
+    <row r="31" spans="1:66" ht="12" customHeight="1" thickBot="1">
+      <c r="A31" s="121"/>
+      <c r="B31" s="195"/>
+      <c r="C31" s="196"/>
+      <c r="D31" s="197"/>
+      <c r="E31" s="198"/>
+      <c r="F31" s="199"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="20"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11"/>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11"/>
+      <c r="R31" s="11"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="63"/>
+      <c r="W31" s="63"/>
+      <c r="X31" s="63"/>
+      <c r="Y31" s="63"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
+      <c r="AC31" s="63"/>
+      <c r="AD31" s="63"/>
+      <c r="AE31" s="63"/>
+      <c r="AF31" s="63"/>
+      <c r="AG31" s="14"/>
+      <c r="AH31" s="20"/>
+      <c r="AI31" s="63"/>
+      <c r="AJ31" s="75"/>
+      <c r="AK31" s="86"/>
+      <c r="AL31" s="63"/>
+      <c r="AM31" s="63"/>
+      <c r="AN31" s="14"/>
+      <c r="AO31" s="20"/>
+      <c r="AP31" s="63"/>
+      <c r="AQ31" s="63"/>
+      <c r="AR31" s="63"/>
+      <c r="AS31" s="63"/>
+      <c r="AT31" s="63"/>
+      <c r="AU31" s="14"/>
+      <c r="AV31" s="20"/>
+      <c r="AW31" s="20"/>
+      <c r="AX31" s="63"/>
+      <c r="AY31" s="63"/>
+      <c r="AZ31" s="63"/>
+      <c r="BA31" s="63"/>
+      <c r="BB31" s="14"/>
+      <c r="BC31" s="20"/>
+      <c r="BD31" s="63"/>
+      <c r="BE31" s="63"/>
+      <c r="BF31" s="63"/>
+      <c r="BG31" s="63"/>
+      <c r="BH31" s="63"/>
+      <c r="BI31" s="14"/>
+      <c r="BJ31" s="20"/>
+      <c r="BK31" s="99"/>
+      <c r="BL31" s="99"/>
+      <c r="BM31" s="99"/>
+      <c r="BN31" s="100"/>
     </row>
-    <row r="32" spans="1:66" ht="12" customHeight="1">
-      <c r="A32" s="121">
-        <v>15</v>
-      </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="134" t="s">
+    <row r="32" spans="1:66">
+      <c r="Z32" s="5"/>
+      <c r="AA32" s="5"/>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="27"/>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="28"/>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="107"/>
+      <c r="B35" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="D32" s="135"/>
-      <c r="E32" s="138" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="140"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="58"/>
-      <c r="O32" s="58"/>
-      <c r="P32" s="58"/>
-      <c r="Q32" s="58"/>
-      <c r="R32" s="58"/>
-      <c r="S32" s="25"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="26"/>
-      <c r="V32" s="58"/>
-      <c r="W32" s="58"/>
-      <c r="X32" s="58"/>
-      <c r="Y32" s="58"/>
-      <c r="Z32" s="25"/>
-      <c r="AA32" s="26"/>
-      <c r="AB32" s="26"/>
-      <c r="AC32" s="58"/>
-      <c r="AD32" s="58"/>
-      <c r="AE32" s="58"/>
-      <c r="AF32" s="58"/>
-      <c r="AG32" s="25"/>
-      <c r="AH32" s="26"/>
-      <c r="AI32" s="58"/>
-      <c r="AJ32" s="71"/>
-      <c r="AK32" s="82"/>
-      <c r="AL32" s="58"/>
-      <c r="AM32" s="58"/>
-      <c r="AN32" s="25"/>
-      <c r="AO32" s="26"/>
-      <c r="AP32" s="58"/>
-      <c r="AQ32" s="58"/>
-      <c r="AR32" s="58"/>
-      <c r="AS32" s="58"/>
-      <c r="AT32" s="58"/>
-      <c r="AU32" s="25"/>
-      <c r="AV32" s="26"/>
-      <c r="AW32" s="26"/>
-      <c r="AX32" s="93"/>
-      <c r="AY32" s="93"/>
-      <c r="AZ32" s="93"/>
-      <c r="BA32" s="93"/>
-      <c r="BB32" s="25"/>
-      <c r="BC32" s="26"/>
-      <c r="BD32" s="110"/>
-      <c r="BE32" s="93"/>
-      <c r="BF32" s="93"/>
-      <c r="BG32" s="93"/>
-      <c r="BH32" s="93"/>
-      <c r="BI32" s="25"/>
-      <c r="BJ32" s="26"/>
-      <c r="BK32" s="58"/>
-      <c r="BL32" s="58"/>
-      <c r="BM32" s="58"/>
-      <c r="BN32" s="71"/>
-    </row>
-    <row r="33" spans="1:66" ht="12" customHeight="1">
-      <c r="A33" s="133"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="136"/>
-      <c r="D33" s="137"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="141"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="23"/>
-      <c r="N33" s="62"/>
-      <c r="O33" s="62"/>
-      <c r="P33" s="62"/>
-      <c r="Q33" s="62"/>
-      <c r="R33" s="62"/>
-      <c r="S33" s="17"/>
-      <c r="T33" s="23"/>
-      <c r="U33" s="23"/>
-      <c r="V33" s="62"/>
-      <c r="W33" s="62"/>
-      <c r="X33" s="62"/>
-      <c r="Y33" s="62"/>
-      <c r="Z33" s="17"/>
-      <c r="AA33" s="23"/>
-      <c r="AB33" s="23"/>
-      <c r="AC33" s="62"/>
-      <c r="AD33" s="62"/>
-      <c r="AE33" s="62"/>
-      <c r="AF33" s="62"/>
-      <c r="AG33" s="17"/>
-      <c r="AH33" s="23"/>
-      <c r="AI33" s="62"/>
-      <c r="AJ33" s="72"/>
-      <c r="AK33" s="83"/>
-      <c r="AL33" s="62"/>
-      <c r="AM33" s="62"/>
-      <c r="AN33" s="17"/>
-      <c r="AO33" s="23"/>
-      <c r="AP33" s="62"/>
-      <c r="AQ33" s="62"/>
-      <c r="AR33" s="62"/>
-      <c r="AS33" s="62"/>
-      <c r="AT33" s="62"/>
-      <c r="AU33" s="17"/>
-      <c r="AV33" s="23"/>
-      <c r="AW33" s="23"/>
-      <c r="AX33" s="62"/>
-      <c r="AY33" s="62"/>
-      <c r="AZ33" s="62"/>
-      <c r="BA33" s="62"/>
-      <c r="BB33" s="17"/>
-      <c r="BC33" s="23"/>
-      <c r="BD33" s="98"/>
-      <c r="BE33" s="98"/>
-      <c r="BF33" s="98"/>
-      <c r="BG33" s="98"/>
-      <c r="BH33" s="98"/>
-      <c r="BI33" s="17"/>
-      <c r="BJ33" s="23"/>
-      <c r="BK33" s="62"/>
-      <c r="BL33" s="62"/>
-      <c r="BM33" s="62"/>
-      <c r="BN33" s="72"/>
-    </row>
-    <row r="34" spans="1:66" ht="12" customHeight="1">
-      <c r="A34" s="121">
-        <v>16</v>
-      </c>
-      <c r="B34" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="142" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="143"/>
-      <c r="E34" s="129" t="s">
-        <v>36</v>
-      </c>
-      <c r="F34" s="131"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="59"/>
-      <c r="O34" s="59"/>
-      <c r="P34" s="59"/>
-      <c r="Q34" s="59"/>
-      <c r="R34" s="59"/>
-      <c r="S34" s="15"/>
-      <c r="T34" s="21"/>
-      <c r="U34" s="21"/>
-      <c r="V34" s="59"/>
-      <c r="W34" s="59"/>
-      <c r="X34" s="59"/>
-      <c r="Y34" s="59"/>
-      <c r="Z34" s="15"/>
-      <c r="AA34" s="21"/>
-      <c r="AB34" s="21"/>
-      <c r="AC34" s="59"/>
-      <c r="AD34" s="59"/>
-      <c r="AE34" s="59"/>
-      <c r="AF34" s="59"/>
-      <c r="AG34" s="15"/>
-      <c r="AH34" s="21"/>
-      <c r="AI34" s="59"/>
-      <c r="AJ34" s="73"/>
-      <c r="AK34" s="84"/>
-      <c r="AL34" s="59"/>
-      <c r="AM34" s="59"/>
-      <c r="AN34" s="15"/>
-      <c r="AO34" s="21"/>
-      <c r="AP34" s="59"/>
-      <c r="AQ34" s="59"/>
-      <c r="AR34" s="59"/>
-      <c r="AS34" s="59"/>
-      <c r="AT34" s="59"/>
-      <c r="AU34" s="15"/>
-      <c r="AV34" s="21"/>
-      <c r="AW34" s="21"/>
-      <c r="AX34" s="59"/>
-      <c r="AY34" s="59"/>
-      <c r="AZ34" s="59"/>
-      <c r="BA34" s="59"/>
-      <c r="BB34" s="15"/>
-      <c r="BC34" s="21"/>
-      <c r="BD34" s="91"/>
-      <c r="BE34" s="91"/>
-      <c r="BF34" s="91"/>
-      <c r="BG34" s="91"/>
-      <c r="BH34" s="91"/>
-      <c r="BI34" s="15"/>
-      <c r="BJ34" s="21"/>
-      <c r="BK34" s="91"/>
-      <c r="BL34" s="91"/>
-      <c r="BM34" s="91"/>
-      <c r="BN34" s="99"/>
-    </row>
-    <row r="35" spans="1:66" ht="12" customHeight="1">
-      <c r="A35" s="133"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="145"/>
-      <c r="E35" s="146"/>
-      <c r="F35" s="147"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="57"/>
-      <c r="O35" s="57"/>
-      <c r="P35" s="57"/>
-      <c r="Q35" s="57"/>
-      <c r="R35" s="57"/>
-      <c r="S35" s="13"/>
-      <c r="T35" s="19"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="57"/>
-      <c r="W35" s="57"/>
-      <c r="X35" s="57"/>
-      <c r="Y35" s="57"/>
-      <c r="Z35" s="13"/>
-      <c r="AA35" s="19"/>
-      <c r="AB35" s="19"/>
-      <c r="AC35" s="57"/>
-      <c r="AD35" s="57"/>
-      <c r="AE35" s="57"/>
-      <c r="AF35" s="57"/>
-      <c r="AG35" s="13"/>
-      <c r="AH35" s="19"/>
-      <c r="AI35" s="57"/>
-      <c r="AJ35" s="74"/>
-      <c r="AK35" s="85"/>
-      <c r="AL35" s="57"/>
-      <c r="AM35" s="57"/>
-      <c r="AN35" s="13"/>
-      <c r="AO35" s="19"/>
-      <c r="AP35" s="57"/>
-      <c r="AQ35" s="57"/>
-      <c r="AR35" s="57"/>
-      <c r="AS35" s="57"/>
-      <c r="AT35" s="57"/>
-      <c r="AU35" s="13"/>
-      <c r="AV35" s="19"/>
-      <c r="AW35" s="19"/>
-      <c r="AX35" s="57"/>
-      <c r="AY35" s="57"/>
-      <c r="AZ35" s="57"/>
-      <c r="BA35" s="57"/>
-      <c r="BB35" s="13"/>
-      <c r="BC35" s="19"/>
-      <c r="BD35" s="57"/>
-      <c r="BE35" s="57"/>
-      <c r="BF35" s="57"/>
-      <c r="BG35" s="57"/>
-      <c r="BH35" s="57"/>
-      <c r="BI35" s="13"/>
-      <c r="BJ35" s="19"/>
-      <c r="BK35" s="92"/>
-      <c r="BL35" s="92"/>
-      <c r="BM35" s="92"/>
-      <c r="BN35" s="94"/>
-    </row>
-    <row r="36" spans="1:66" ht="12" customHeight="1">
-      <c r="A36" s="121">
-        <v>17</v>
-      </c>
-      <c r="B36" s="123" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="125" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="126"/>
-      <c r="E36" s="129" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36" s="131"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="21"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="15"/>
-      <c r="T36" s="21"/>
-      <c r="U36" s="21"/>
-      <c r="V36" s="59"/>
-      <c r="W36" s="59"/>
-      <c r="X36" s="59"/>
-      <c r="Y36" s="59"/>
-      <c r="Z36" s="15"/>
-      <c r="AA36" s="21"/>
-      <c r="AB36" s="21"/>
-      <c r="AC36" s="59"/>
-      <c r="AD36" s="59"/>
-      <c r="AE36" s="59"/>
-      <c r="AF36" s="59"/>
-      <c r="AG36" s="15"/>
-      <c r="AH36" s="21"/>
-      <c r="AI36" s="59"/>
-      <c r="AJ36" s="73"/>
-      <c r="AK36" s="84"/>
-      <c r="AL36" s="59"/>
-      <c r="AM36" s="59"/>
-      <c r="AN36" s="15"/>
-      <c r="AO36" s="21"/>
-      <c r="AP36" s="59"/>
-      <c r="AQ36" s="59"/>
-      <c r="AR36" s="59"/>
-      <c r="AS36" s="59"/>
-      <c r="AT36" s="59"/>
-      <c r="AU36" s="15"/>
-      <c r="AV36" s="21"/>
-      <c r="AW36" s="21"/>
-      <c r="AX36" s="59"/>
-      <c r="AY36" s="59"/>
-      <c r="AZ36" s="59"/>
-      <c r="BA36" s="59"/>
-      <c r="BB36" s="15"/>
-      <c r="BC36" s="21"/>
-      <c r="BD36" s="59"/>
-      <c r="BE36" s="59"/>
-      <c r="BF36" s="59"/>
-      <c r="BG36" s="91"/>
-      <c r="BH36" s="91"/>
-      <c r="BI36" s="15"/>
-      <c r="BJ36" s="21"/>
-      <c r="BK36" s="91"/>
-      <c r="BL36" s="91"/>
-      <c r="BM36" s="91"/>
-      <c r="BN36" s="99"/>
-    </row>
-    <row r="37" spans="1:66" ht="12" customHeight="1" thickBot="1">
-      <c r="A37" s="122"/>
-      <c r="B37" s="124"/>
-      <c r="C37" s="127"/>
-      <c r="D37" s="128"/>
-      <c r="E37" s="130"/>
-      <c r="F37" s="132"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
-      <c r="R37" s="11"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
-      <c r="V37" s="63"/>
-      <c r="W37" s="63"/>
-      <c r="X37" s="63"/>
-      <c r="Y37" s="63"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="20"/>
-      <c r="AB37" s="20"/>
-      <c r="AC37" s="63"/>
-      <c r="AD37" s="63"/>
-      <c r="AE37" s="63"/>
-      <c r="AF37" s="63"/>
-      <c r="AG37" s="14"/>
-      <c r="AH37" s="20"/>
-      <c r="AI37" s="63"/>
-      <c r="AJ37" s="75"/>
-      <c r="AK37" s="86"/>
-      <c r="AL37" s="63"/>
-      <c r="AM37" s="63"/>
-      <c r="AN37" s="14"/>
-      <c r="AO37" s="20"/>
-      <c r="AP37" s="63"/>
-      <c r="AQ37" s="63"/>
-      <c r="AR37" s="63"/>
-      <c r="AS37" s="63"/>
-      <c r="AT37" s="63"/>
-      <c r="AU37" s="14"/>
-      <c r="AV37" s="20"/>
-      <c r="AW37" s="20"/>
-      <c r="AX37" s="63"/>
-      <c r="AY37" s="63"/>
-      <c r="AZ37" s="63"/>
-      <c r="BA37" s="63"/>
-      <c r="BB37" s="14"/>
-      <c r="BC37" s="20"/>
-      <c r="BD37" s="63"/>
-      <c r="BE37" s="63"/>
-      <c r="BF37" s="63"/>
-      <c r="BG37" s="63"/>
-      <c r="BH37" s="63"/>
-      <c r="BI37" s="14"/>
-      <c r="BJ37" s="20"/>
-      <c r="BK37" s="100"/>
-      <c r="BL37" s="100"/>
-      <c r="BM37" s="100"/>
-      <c r="BN37" s="101"/>
-    </row>
-    <row r="38" spans="1:66">
-      <c r="Z38" s="5"/>
-      <c r="AA38" s="5"/>
-    </row>
-    <row r="39" spans="1:66">
-      <c r="A39" s="27"/>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:66">
-      <c r="A40" s="28"/>
-      <c r="B40" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:66">
-      <c r="A41" s="108"/>
-      <c r="B41" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="76">
+  <mergeCells count="64">
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
     <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="C28:D29"/>
     <mergeCell ref="E28:E29"/>
-    <mergeCell ref="E30:E31"/>
     <mergeCell ref="F28:F29"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="F26:F27"/>
@@ -5657,66 +5215,6 @@
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="C26:D27"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="C34:D35"/>
-    <mergeCell ref="E34:E35"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/01_要件定義/03_WBS.xlsx
+++ b/01_要件定義/03_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\01_要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65171AA7-AE69-4812-87B8-1E7720937B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0F2BCF-E1E3-4C4A-AAB2-CED1E467219E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1435,7 +1435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1786,35 +1786,185 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1879,154 +2029,7 @@
     <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2591,94 +2594,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="136" t="s">
+      <c r="B1" s="186" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="139" t="s">
+      <c r="C1" s="189" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="140"/>
-      <c r="E1" s="145" t="s">
+      <c r="D1" s="190"/>
+      <c r="E1" s="195" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="148" t="s">
+      <c r="F1" s="198" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="130">
+      <c r="G1" s="180">
         <v>45536</v>
       </c>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="131"/>
-      <c r="M1" s="131"/>
-      <c r="N1" s="131"/>
-      <c r="O1" s="131"/>
-      <c r="P1" s="131"/>
-      <c r="Q1" s="131"/>
-      <c r="R1" s="131"/>
-      <c r="S1" s="131"/>
-      <c r="T1" s="131"/>
-      <c r="U1" s="131"/>
-      <c r="V1" s="131"/>
-      <c r="W1" s="131"/>
-      <c r="X1" s="131"/>
-      <c r="Y1" s="131"/>
-      <c r="Z1" s="131"/>
-      <c r="AA1" s="131"/>
-      <c r="AB1" s="131"/>
-      <c r="AC1" s="131"/>
-      <c r="AD1" s="131"/>
-      <c r="AE1" s="131"/>
-      <c r="AF1" s="131"/>
-      <c r="AG1" s="131"/>
-      <c r="AH1" s="131"/>
-      <c r="AI1" s="131"/>
-      <c r="AJ1" s="132"/>
-      <c r="AK1" s="130">
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="181"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="181"/>
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="181"/>
+      <c r="T1" s="181"/>
+      <c r="U1" s="181"/>
+      <c r="V1" s="181"/>
+      <c r="W1" s="181"/>
+      <c r="X1" s="181"/>
+      <c r="Y1" s="181"/>
+      <c r="Z1" s="181"/>
+      <c r="AA1" s="181"/>
+      <c r="AB1" s="181"/>
+      <c r="AC1" s="181"/>
+      <c r="AD1" s="181"/>
+      <c r="AE1" s="181"/>
+      <c r="AF1" s="181"/>
+      <c r="AG1" s="181"/>
+      <c r="AH1" s="181"/>
+      <c r="AI1" s="181"/>
+      <c r="AJ1" s="182"/>
+      <c r="AK1" s="180">
         <v>45566</v>
       </c>
-      <c r="AL1" s="131"/>
-      <c r="AM1" s="131"/>
-      <c r="AN1" s="131"/>
-      <c r="AO1" s="131"/>
-      <c r="AP1" s="131"/>
-      <c r="AQ1" s="131"/>
-      <c r="AR1" s="131"/>
-      <c r="AS1" s="131"/>
-      <c r="AT1" s="131"/>
-      <c r="AU1" s="131"/>
-      <c r="AV1" s="131"/>
-      <c r="AW1" s="131"/>
-      <c r="AX1" s="131"/>
-      <c r="AY1" s="131"/>
-      <c r="AZ1" s="131"/>
-      <c r="BA1" s="131"/>
-      <c r="BB1" s="131"/>
-      <c r="BC1" s="131"/>
-      <c r="BD1" s="131"/>
-      <c r="BE1" s="131"/>
-      <c r="BF1" s="131"/>
-      <c r="BG1" s="131"/>
-      <c r="BH1" s="131"/>
-      <c r="BI1" s="131"/>
-      <c r="BJ1" s="131"/>
-      <c r="BK1" s="131"/>
-      <c r="BL1" s="131"/>
-      <c r="BM1" s="131"/>
-      <c r="BN1" s="132"/>
+      <c r="AL1" s="181"/>
+      <c r="AM1" s="181"/>
+      <c r="AN1" s="181"/>
+      <c r="AO1" s="181"/>
+      <c r="AP1" s="181"/>
+      <c r="AQ1" s="181"/>
+      <c r="AR1" s="181"/>
+      <c r="AS1" s="181"/>
+      <c r="AT1" s="181"/>
+      <c r="AU1" s="181"/>
+      <c r="AV1" s="181"/>
+      <c r="AW1" s="181"/>
+      <c r="AX1" s="181"/>
+      <c r="AY1" s="181"/>
+      <c r="AZ1" s="181"/>
+      <c r="BA1" s="181"/>
+      <c r="BB1" s="181"/>
+      <c r="BC1" s="181"/>
+      <c r="BD1" s="181"/>
+      <c r="BE1" s="181"/>
+      <c r="BF1" s="181"/>
+      <c r="BG1" s="181"/>
+      <c r="BH1" s="181"/>
+      <c r="BI1" s="181"/>
+      <c r="BJ1" s="181"/>
+      <c r="BK1" s="181"/>
+      <c r="BL1" s="181"/>
+      <c r="BM1" s="181"/>
+      <c r="BN1" s="182"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="134"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="149"/>
+      <c r="A2" s="184"/>
+      <c r="B2" s="187"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="196"/>
+      <c r="F2" s="199"/>
       <c r="G2" s="43">
         <v>45537</v>
       </c>
@@ -2920,12 +2923,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="135"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="150"/>
+      <c r="A3" s="185"/>
+      <c r="B3" s="188"/>
+      <c r="C3" s="193"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="197"/>
+      <c r="F3" s="200"/>
       <c r="G3" s="45" t="s">
         <v>14</v>
       </c>
@@ -3108,20 +3111,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="160">
+      <c r="A4" s="173">
         <v>1</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="161" t="s">
+      <c r="C4" s="174" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="162"/>
-      <c r="E4" s="163" t="s">
+      <c r="D4" s="175"/>
+      <c r="E4" s="176" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="165" t="s">
+      <c r="F4" s="178" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="89"/>
@@ -3186,12 +3189,12 @@
       <c r="BN4" s="65"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="152"/>
+      <c r="A5" s="169"/>
       <c r="B5" s="31"/>
-      <c r="C5" s="128"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="164"/>
-      <c r="F5" s="166"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="177"/>
+      <c r="F5" s="179"/>
       <c r="G5" s="90"/>
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
@@ -3254,18 +3257,18 @@
       <c r="BN5" s="66"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="151">
+      <c r="A6" s="168">
         <v>2</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="153" t="s">
+      <c r="C6" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="127"/>
-      <c r="E6" s="156" t="s">
+      <c r="D6" s="146"/>
+      <c r="E6" s="170" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="158" t="s">
+      <c r="F6" s="172" t="s">
         <v>37</v>
       </c>
       <c r="G6" s="47"/>
@@ -3330,12 +3333,12 @@
       <c r="BN6" s="67"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="152"/>
+      <c r="A7" s="169"/>
       <c r="B7" s="31"/>
-      <c r="C7" s="154"/>
-      <c r="D7" s="155"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="159"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="151"/>
+      <c r="E7" s="171"/>
+      <c r="F7" s="138"/>
       <c r="G7" s="48"/>
       <c r="H7" s="101"/>
       <c r="I7" s="58"/>
@@ -3398,20 +3401,20 @@
       <c r="BN7" s="68"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="120">
+      <c r="A8" s="121">
         <v>3</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="167" t="s">
+      <c r="C8" s="158" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="168"/>
-      <c r="E8" s="171" t="s">
+      <c r="D8" s="159"/>
+      <c r="E8" s="162" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="173" t="s">
+      <c r="F8" s="143" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="35"/>
@@ -3476,12 +3479,12 @@
       <c r="BN8" s="69"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="121"/>
+      <c r="A9" s="122"/>
       <c r="B9" s="34"/>
-      <c r="C9" s="169"/>
-      <c r="D9" s="170"/>
-      <c r="E9" s="172"/>
-      <c r="F9" s="174"/>
+      <c r="C9" s="160"/>
+      <c r="D9" s="161"/>
+      <c r="E9" s="157"/>
+      <c r="F9" s="153"/>
       <c r="G9" s="49"/>
       <c r="H9" s="60"/>
       <c r="I9" s="60"/>
@@ -3544,20 +3547,20 @@
       <c r="BN9" s="70"/>
     </row>
     <row r="10" spans="1:66" ht="12" customHeight="1">
-      <c r="A10" s="120">
+      <c r="A10" s="121">
         <v>4</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="163" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="176"/>
-      <c r="E10" s="171" t="s">
+      <c r="D10" s="164"/>
+      <c r="E10" s="162" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="173" t="s">
+      <c r="F10" s="143" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="46"/>
@@ -3622,12 +3625,12 @@
       <c r="BN10" s="66"/>
     </row>
     <row r="11" spans="1:66" ht="12" customHeight="1">
-      <c r="A11" s="121"/>
+      <c r="A11" s="122"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="177"/>
-      <c r="D11" s="178"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="125"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="144"/>
       <c r="G11" s="46"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
@@ -3690,18 +3693,18 @@
       <c r="BN11" s="66"/>
     </row>
     <row r="12" spans="1:66" ht="12" customHeight="1">
-      <c r="A12" s="120">
+      <c r="A12" s="121">
         <v>5</v>
       </c>
       <c r="B12" s="33"/>
-      <c r="C12" s="153" t="s">
+      <c r="C12" s="149" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="127"/>
-      <c r="E12" s="122" t="s">
+      <c r="D12" s="146"/>
+      <c r="E12" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="124" t="s">
+      <c r="F12" s="148" t="s">
         <v>39</v>
       </c>
       <c r="G12" s="47"/>
@@ -3766,12 +3769,12 @@
       <c r="BN12" s="67"/>
     </row>
     <row r="13" spans="1:66" ht="12" customHeight="1">
-      <c r="A13" s="121"/>
+      <c r="A13" s="122"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="179"/>
-      <c r="D13" s="180"/>
-      <c r="E13" s="172"/>
-      <c r="F13" s="174"/>
+      <c r="C13" s="154"/>
+      <c r="D13" s="155"/>
+      <c r="E13" s="157"/>
+      <c r="F13" s="153"/>
       <c r="G13" s="48"/>
       <c r="H13" s="58"/>
       <c r="I13" s="58"/>
@@ -3834,20 +3837,20 @@
       <c r="BN13" s="68"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="120">
+      <c r="A14" s="121">
         <v>6</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="181" t="s">
+      <c r="C14" s="125" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="182"/>
-      <c r="E14" s="183" t="s">
+      <c r="D14" s="126"/>
+      <c r="E14" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="173" t="s">
+      <c r="F14" s="143" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="35"/>
@@ -3912,12 +3915,12 @@
       <c r="BN14" s="69"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="121"/>
+      <c r="A15" s="122"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="128"/>
-      <c r="D15" s="129"/>
-      <c r="E15" s="184"/>
-      <c r="F15" s="125"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="144"/>
       <c r="G15" s="48"/>
       <c r="H15" s="58"/>
       <c r="I15" s="58"/>
@@ -3980,18 +3983,18 @@
       <c r="BN15" s="68"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="120">
+      <c r="A16" s="121">
         <v>7</v>
       </c>
       <c r="B16" s="33"/>
-      <c r="C16" s="153" t="s">
+      <c r="C16" s="149" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="127"/>
-      <c r="E16" s="185" t="s">
+      <c r="D16" s="146"/>
+      <c r="E16" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="124" t="s">
+      <c r="F16" s="148" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="47"/>
@@ -4056,12 +4059,12 @@
       <c r="BN16" s="67"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="121"/>
+      <c r="A17" s="122"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="128"/>
-      <c r="D17" s="129"/>
-      <c r="E17" s="184"/>
-      <c r="F17" s="125"/>
+      <c r="C17" s="139"/>
+      <c r="D17" s="140"/>
+      <c r="E17" s="142"/>
+      <c r="F17" s="144"/>
       <c r="G17" s="48"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -4124,18 +4127,18 @@
       <c r="BN17" s="68"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="120">
+      <c r="A18" s="121">
         <v>8</v>
       </c>
       <c r="B18" s="33"/>
-      <c r="C18" s="153" t="s">
+      <c r="C18" s="149" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="127"/>
-      <c r="E18" s="185" t="s">
+      <c r="D18" s="146"/>
+      <c r="E18" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="124" t="s">
+      <c r="F18" s="148" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="48"/>
@@ -4200,12 +4203,12 @@
       <c r="BN18" s="71"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="121"/>
+      <c r="A19" s="122"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="154"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="186"/>
-      <c r="F19" s="174"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="152"/>
+      <c r="F19" s="153"/>
       <c r="G19" s="50"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -4242,10 +4245,10 @@
       <c r="AN19" s="17"/>
       <c r="AO19" s="23"/>
       <c r="AP19" s="62"/>
-      <c r="AQ19" s="200"/>
-      <c r="AR19" s="200"/>
-      <c r="AS19" s="200"/>
-      <c r="AT19" s="200"/>
+      <c r="AQ19" s="120"/>
+      <c r="AR19" s="120"/>
+      <c r="AS19" s="120"/>
+      <c r="AT19" s="120"/>
       <c r="AU19" s="17"/>
       <c r="AV19" s="23"/>
       <c r="AW19" s="23"/>
@@ -4268,20 +4271,20 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="120">
+      <c r="A20" s="121">
         <v>9</v>
       </c>
       <c r="B20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="181" t="s">
+      <c r="C20" s="125" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="182"/>
-      <c r="E20" s="183" t="s">
+      <c r="D20" s="126"/>
+      <c r="E20" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="173"/>
+      <c r="F20" s="143"/>
       <c r="G20" s="35"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -4344,14 +4347,14 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="121"/>
+      <c r="A21" s="122"/>
       <c r="B21" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="128"/>
-      <c r="D21" s="129"/>
-      <c r="E21" s="184"/>
-      <c r="F21" s="125"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="142"/>
+      <c r="F21" s="144"/>
       <c r="G21" s="47"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -4395,10 +4398,10 @@
       <c r="AU21" s="13"/>
       <c r="AV21" s="19"/>
       <c r="AW21" s="19"/>
-      <c r="AX21" s="57"/>
-      <c r="AY21" s="57"/>
-      <c r="AZ21" s="57"/>
-      <c r="BA21" s="57"/>
+      <c r="AX21" s="201"/>
+      <c r="AY21" s="201"/>
+      <c r="AZ21" s="201"/>
+      <c r="BA21" s="201"/>
       <c r="BB21" s="13"/>
       <c r="BC21" s="19"/>
       <c r="BD21" s="57"/>
@@ -4414,18 +4417,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="120">
+      <c r="A22" s="121">
         <v>10</v>
       </c>
       <c r="B22" s="33"/>
-      <c r="C22" s="126" t="s">
+      <c r="C22" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="127"/>
-      <c r="E22" s="185" t="s">
+      <c r="D22" s="146"/>
+      <c r="E22" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="124"/>
+      <c r="F22" s="148"/>
       <c r="G22" s="47"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4488,12 +4491,12 @@
       <c r="BN22" s="74"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="121"/>
+      <c r="A23" s="122"/>
       <c r="B23" s="33"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="129"/>
-      <c r="E23" s="184"/>
-      <c r="F23" s="125"/>
+      <c r="C23" s="139"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="142"/>
+      <c r="F23" s="144"/>
       <c r="G23" s="47"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -4537,10 +4540,10 @@
       <c r="AU23" s="13"/>
       <c r="AV23" s="19"/>
       <c r="AW23" s="19"/>
-      <c r="AX23" s="57"/>
-      <c r="AY23" s="57"/>
-      <c r="AZ23" s="57"/>
-      <c r="BA23" s="57"/>
+      <c r="AX23" s="201"/>
+      <c r="AY23" s="201"/>
+      <c r="AZ23" s="201"/>
+      <c r="BA23" s="201"/>
       <c r="BB23" s="13"/>
       <c r="BC23" s="19"/>
       <c r="BD23" s="57"/>
@@ -4556,18 +4559,18 @@
       <c r="BN23" s="74"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="120">
+      <c r="A24" s="121">
         <v>11</v>
       </c>
       <c r="B24" s="33"/>
-      <c r="C24" s="126" t="s">
+      <c r="C24" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="127"/>
-      <c r="E24" s="122" t="s">
+      <c r="D24" s="146"/>
+      <c r="E24" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="124"/>
+      <c r="F24" s="148"/>
       <c r="G24" s="48"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -4630,12 +4633,12 @@
       <c r="BN24" s="71"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="121"/>
+      <c r="A25" s="122"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="129"/>
-      <c r="E25" s="123"/>
-      <c r="F25" s="125"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="144"/>
       <c r="G25" s="48"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
@@ -4679,10 +4682,10 @@
       <c r="AU25" s="25"/>
       <c r="AV25" s="26"/>
       <c r="AW25" s="26"/>
-      <c r="AX25" s="58"/>
-      <c r="AY25" s="58"/>
-      <c r="AZ25" s="58"/>
-      <c r="BA25" s="58"/>
+      <c r="AX25" s="101"/>
+      <c r="AY25" s="101"/>
+      <c r="AZ25" s="101"/>
+      <c r="BA25" s="101"/>
       <c r="BB25" s="25"/>
       <c r="BC25" s="26"/>
       <c r="BD25" s="58"/>
@@ -4698,18 +4701,18 @@
       <c r="BN25" s="71"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="120">
+      <c r="A26" s="121">
         <v>12</v>
       </c>
       <c r="B26" s="33"/>
-      <c r="C26" s="126" t="s">
+      <c r="C26" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="127"/>
-      <c r="E26" s="122" t="s">
+      <c r="D26" s="146"/>
+      <c r="E26" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="124"/>
+      <c r="F26" s="148"/>
       <c r="G26" s="48"/>
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
@@ -4772,12 +4775,12 @@
       <c r="BN26" s="71"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="121"/>
+      <c r="A27" s="122"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="128"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="125"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="140"/>
+      <c r="E27" s="167"/>
+      <c r="F27" s="144"/>
       <c r="G27" s="48"/>
       <c r="H27" s="24"/>
       <c r="I27" s="24"/>
@@ -4821,10 +4824,10 @@
       <c r="AU27" s="25"/>
       <c r="AV27" s="26"/>
       <c r="AW27" s="26"/>
-      <c r="AX27" s="93"/>
-      <c r="AY27" s="93"/>
-      <c r="AZ27" s="93"/>
-      <c r="BA27" s="93"/>
+      <c r="AX27" s="101"/>
+      <c r="AY27" s="101"/>
+      <c r="AZ27" s="101"/>
+      <c r="BA27" s="101"/>
       <c r="BB27" s="25"/>
       <c r="BC27" s="26"/>
       <c r="BD27" s="58"/>
@@ -4840,20 +4843,20 @@
       <c r="BN27" s="71"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="120">
+      <c r="A28" s="121">
         <v>13</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="187" t="s">
+      <c r="C28" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="188"/>
-      <c r="E28" s="191" t="s">
+      <c r="D28" s="134"/>
+      <c r="E28" s="129" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="193"/>
+      <c r="F28" s="131"/>
       <c r="G28" s="35"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -4916,12 +4919,12 @@
       <c r="BN28" s="98"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="121"/>
+      <c r="A29" s="122"/>
       <c r="B29" s="31"/>
-      <c r="C29" s="189"/>
-      <c r="D29" s="190"/>
-      <c r="E29" s="192"/>
-      <c r="F29" s="159"/>
+      <c r="C29" s="135"/>
+      <c r="D29" s="136"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="138"/>
       <c r="G29" s="47"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -4984,20 +4987,20 @@
       <c r="BN29" s="94"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="120">
+      <c r="A30" s="121">
         <v>14</v>
       </c>
-      <c r="B30" s="194" t="s">
+      <c r="B30" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="181" t="s">
+      <c r="C30" s="125" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="182"/>
-      <c r="E30" s="191" t="s">
+      <c r="D30" s="126"/>
+      <c r="E30" s="129" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="193"/>
+      <c r="F30" s="131"/>
       <c r="G30" s="35"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
@@ -5060,12 +5063,12 @@
       <c r="BN30" s="98"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1" thickBot="1">
-      <c r="A31" s="121"/>
-      <c r="B31" s="195"/>
-      <c r="C31" s="196"/>
-      <c r="D31" s="197"/>
-      <c r="E31" s="198"/>
-      <c r="F31" s="199"/>
+      <c r="A31" s="122"/>
+      <c r="B31" s="124"/>
+      <c r="C31" s="127"/>
+      <c r="D31" s="128"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="132"/>
       <c r="G31" s="36"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -5151,11 +5154,49 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="C28:D29"/>
     <mergeCell ref="E28:E29"/>
@@ -5168,53 +5209,15 @@
     <mergeCell ref="C22:D23"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="C24:D25"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/01_要件定義/03_WBS.xlsx
+++ b/01_要件定義/03_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\01_要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0F2BCF-E1E3-4C4A-AAB2-CED1E467219E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB7CD0C-7FEA-4929-963E-63E2963069DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1789,248 +1789,248 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2594,94 +2594,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="183" t="s">
+      <c r="A1" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="186" t="s">
+      <c r="B1" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="189" t="s">
+      <c r="C1" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="190"/>
-      <c r="E1" s="195" t="s">
+      <c r="D1" s="142"/>
+      <c r="E1" s="147" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="198" t="s">
+      <c r="F1" s="150" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="180">
+      <c r="G1" s="132">
         <v>45536</v>
       </c>
-      <c r="H1" s="181"/>
-      <c r="I1" s="181"/>
-      <c r="J1" s="181"/>
-      <c r="K1" s="181"/>
-      <c r="L1" s="181"/>
-      <c r="M1" s="181"/>
-      <c r="N1" s="181"/>
-      <c r="O1" s="181"/>
-      <c r="P1" s="181"/>
-      <c r="Q1" s="181"/>
-      <c r="R1" s="181"/>
-      <c r="S1" s="181"/>
-      <c r="T1" s="181"/>
-      <c r="U1" s="181"/>
-      <c r="V1" s="181"/>
-      <c r="W1" s="181"/>
-      <c r="X1" s="181"/>
-      <c r="Y1" s="181"/>
-      <c r="Z1" s="181"/>
-      <c r="AA1" s="181"/>
-      <c r="AB1" s="181"/>
-      <c r="AC1" s="181"/>
-      <c r="AD1" s="181"/>
-      <c r="AE1" s="181"/>
-      <c r="AF1" s="181"/>
-      <c r="AG1" s="181"/>
-      <c r="AH1" s="181"/>
-      <c r="AI1" s="181"/>
-      <c r="AJ1" s="182"/>
-      <c r="AK1" s="180">
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="133"/>
+      <c r="W1" s="133"/>
+      <c r="X1" s="133"/>
+      <c r="Y1" s="133"/>
+      <c r="Z1" s="133"/>
+      <c r="AA1" s="133"/>
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="133"/>
+      <c r="AD1" s="133"/>
+      <c r="AE1" s="133"/>
+      <c r="AF1" s="133"/>
+      <c r="AG1" s="133"/>
+      <c r="AH1" s="133"/>
+      <c r="AI1" s="133"/>
+      <c r="AJ1" s="134"/>
+      <c r="AK1" s="132">
         <v>45566</v>
       </c>
-      <c r="AL1" s="181"/>
-      <c r="AM1" s="181"/>
-      <c r="AN1" s="181"/>
-      <c r="AO1" s="181"/>
-      <c r="AP1" s="181"/>
-      <c r="AQ1" s="181"/>
-      <c r="AR1" s="181"/>
-      <c r="AS1" s="181"/>
-      <c r="AT1" s="181"/>
-      <c r="AU1" s="181"/>
-      <c r="AV1" s="181"/>
-      <c r="AW1" s="181"/>
-      <c r="AX1" s="181"/>
-      <c r="AY1" s="181"/>
-      <c r="AZ1" s="181"/>
-      <c r="BA1" s="181"/>
-      <c r="BB1" s="181"/>
-      <c r="BC1" s="181"/>
-      <c r="BD1" s="181"/>
-      <c r="BE1" s="181"/>
-      <c r="BF1" s="181"/>
-      <c r="BG1" s="181"/>
-      <c r="BH1" s="181"/>
-      <c r="BI1" s="181"/>
-      <c r="BJ1" s="181"/>
-      <c r="BK1" s="181"/>
-      <c r="BL1" s="181"/>
-      <c r="BM1" s="181"/>
-      <c r="BN1" s="182"/>
+      <c r="AL1" s="133"/>
+      <c r="AM1" s="133"/>
+      <c r="AN1" s="133"/>
+      <c r="AO1" s="133"/>
+      <c r="AP1" s="133"/>
+      <c r="AQ1" s="133"/>
+      <c r="AR1" s="133"/>
+      <c r="AS1" s="133"/>
+      <c r="AT1" s="133"/>
+      <c r="AU1" s="133"/>
+      <c r="AV1" s="133"/>
+      <c r="AW1" s="133"/>
+      <c r="AX1" s="133"/>
+      <c r="AY1" s="133"/>
+      <c r="AZ1" s="133"/>
+      <c r="BA1" s="133"/>
+      <c r="BB1" s="133"/>
+      <c r="BC1" s="133"/>
+      <c r="BD1" s="133"/>
+      <c r="BE1" s="133"/>
+      <c r="BF1" s="133"/>
+      <c r="BG1" s="133"/>
+      <c r="BH1" s="133"/>
+      <c r="BI1" s="133"/>
+      <c r="BJ1" s="133"/>
+      <c r="BK1" s="133"/>
+      <c r="BL1" s="133"/>
+      <c r="BM1" s="133"/>
+      <c r="BN1" s="134"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="184"/>
-      <c r="B2" s="187"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="199"/>
+      <c r="A2" s="136"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="151"/>
       <c r="G2" s="43">
         <v>45537</v>
       </c>
@@ -2923,12 +2923,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="185"/>
-      <c r="B3" s="188"/>
-      <c r="C3" s="193"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="200"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="146"/>
+      <c r="E3" s="149"/>
+      <c r="F3" s="152"/>
       <c r="G3" s="45" t="s">
         <v>14</v>
       </c>
@@ -3111,20 +3111,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="173">
+      <c r="A4" s="162">
         <v>1</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="174" t="s">
+      <c r="C4" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="175"/>
-      <c r="E4" s="176" t="s">
+      <c r="D4" s="164"/>
+      <c r="E4" s="165" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="178" t="s">
+      <c r="F4" s="167" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="89"/>
@@ -3189,12 +3189,12 @@
       <c r="BN4" s="65"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="169"/>
+      <c r="A5" s="154"/>
       <c r="B5" s="31"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="177"/>
-      <c r="F5" s="179"/>
+      <c r="C5" s="130"/>
+      <c r="D5" s="131"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="168"/>
       <c r="G5" s="90"/>
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
@@ -3257,18 +3257,18 @@
       <c r="BN5" s="66"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="168">
+      <c r="A6" s="153">
         <v>2</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="149" t="s">
+      <c r="C6" s="155" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="146"/>
-      <c r="E6" s="170" t="s">
+      <c r="D6" s="129"/>
+      <c r="E6" s="158" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="172" t="s">
+      <c r="F6" s="160" t="s">
         <v>37</v>
       </c>
       <c r="G6" s="47"/>
@@ -3333,12 +3333,12 @@
       <c r="BN6" s="67"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="169"/>
+      <c r="A7" s="154"/>
       <c r="B7" s="31"/>
-      <c r="C7" s="150"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="171"/>
-      <c r="F7" s="138"/>
+      <c r="C7" s="156"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="161"/>
       <c r="G7" s="48"/>
       <c r="H7" s="101"/>
       <c r="I7" s="58"/>
@@ -3401,20 +3401,20 @@
       <c r="BN7" s="68"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="121">
+      <c r="A8" s="122">
         <v>3</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="158" t="s">
+      <c r="C8" s="169" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="159"/>
-      <c r="E8" s="162" t="s">
+      <c r="D8" s="170"/>
+      <c r="E8" s="173" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="143" t="s">
+      <c r="F8" s="175" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="35"/>
@@ -3479,12 +3479,12 @@
       <c r="BN8" s="69"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="122"/>
+      <c r="A9" s="123"/>
       <c r="B9" s="34"/>
-      <c r="C9" s="160"/>
-      <c r="D9" s="161"/>
-      <c r="E9" s="157"/>
-      <c r="F9" s="153"/>
+      <c r="C9" s="171"/>
+      <c r="D9" s="172"/>
+      <c r="E9" s="174"/>
+      <c r="F9" s="176"/>
       <c r="G9" s="49"/>
       <c r="H9" s="60"/>
       <c r="I9" s="60"/>
@@ -3547,20 +3547,20 @@
       <c r="BN9" s="70"/>
     </row>
     <row r="10" spans="1:66" ht="12" customHeight="1">
-      <c r="A10" s="121">
+      <c r="A10" s="122">
         <v>4</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="163" t="s">
+      <c r="C10" s="177" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="164"/>
-      <c r="E10" s="162" t="s">
+      <c r="D10" s="178"/>
+      <c r="E10" s="173" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="143" t="s">
+      <c r="F10" s="175" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="46"/>
@@ -3625,12 +3625,12 @@
       <c r="BN10" s="66"/>
     </row>
     <row r="11" spans="1:66" ht="12" customHeight="1">
-      <c r="A11" s="122"/>
+      <c r="A11" s="123"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="166"/>
-      <c r="E11" s="167"/>
-      <c r="F11" s="144"/>
+      <c r="C11" s="179"/>
+      <c r="D11" s="180"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="127"/>
       <c r="G11" s="46"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
@@ -3693,18 +3693,18 @@
       <c r="BN11" s="66"/>
     </row>
     <row r="12" spans="1:66" ht="12" customHeight="1">
-      <c r="A12" s="121">
+      <c r="A12" s="122">
         <v>5</v>
       </c>
       <c r="B12" s="33"/>
-      <c r="C12" s="149" t="s">
+      <c r="C12" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="146"/>
-      <c r="E12" s="156" t="s">
+      <c r="D12" s="129"/>
+      <c r="E12" s="124" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="148" t="s">
+      <c r="F12" s="126" t="s">
         <v>39</v>
       </c>
       <c r="G12" s="47"/>
@@ -3769,12 +3769,12 @@
       <c r="BN12" s="67"/>
     </row>
     <row r="13" spans="1:66" ht="12" customHeight="1">
-      <c r="A13" s="122"/>
+      <c r="A13" s="123"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="154"/>
-      <c r="D13" s="155"/>
-      <c r="E13" s="157"/>
-      <c r="F13" s="153"/>
+      <c r="C13" s="181"/>
+      <c r="D13" s="182"/>
+      <c r="E13" s="174"/>
+      <c r="F13" s="176"/>
       <c r="G13" s="48"/>
       <c r="H13" s="58"/>
       <c r="I13" s="58"/>
@@ -3837,20 +3837,20 @@
       <c r="BN13" s="68"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="121">
+      <c r="A14" s="122">
         <v>6</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="125" t="s">
+      <c r="C14" s="183" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="126"/>
-      <c r="E14" s="141" t="s">
+      <c r="D14" s="184"/>
+      <c r="E14" s="185" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="143" t="s">
+      <c r="F14" s="175" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="35"/>
@@ -3915,12 +3915,12 @@
       <c r="BN14" s="69"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="122"/>
+      <c r="A15" s="123"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="139"/>
-      <c r="D15" s="140"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="144"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="186"/>
+      <c r="F15" s="127"/>
       <c r="G15" s="48"/>
       <c r="H15" s="58"/>
       <c r="I15" s="58"/>
@@ -3983,18 +3983,18 @@
       <c r="BN15" s="68"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="121">
+      <c r="A16" s="122">
         <v>7</v>
       </c>
       <c r="B16" s="33"/>
-      <c r="C16" s="149" t="s">
+      <c r="C16" s="155" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="146"/>
-      <c r="E16" s="147" t="s">
+      <c r="D16" s="129"/>
+      <c r="E16" s="187" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="148" t="s">
+      <c r="F16" s="126" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="47"/>
@@ -4059,12 +4059,12 @@
       <c r="BN16" s="67"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="122"/>
+      <c r="A17" s="123"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="139"/>
-      <c r="D17" s="140"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="144"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="131"/>
+      <c r="E17" s="186"/>
+      <c r="F17" s="127"/>
       <c r="G17" s="48"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -4127,18 +4127,18 @@
       <c r="BN17" s="68"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="121">
+      <c r="A18" s="122">
         <v>8</v>
       </c>
       <c r="B18" s="33"/>
-      <c r="C18" s="149" t="s">
+      <c r="C18" s="155" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="146"/>
-      <c r="E18" s="147" t="s">
+      <c r="D18" s="129"/>
+      <c r="E18" s="187" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="148" t="s">
+      <c r="F18" s="126" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="48"/>
@@ -4203,12 +4203,12 @@
       <c r="BN18" s="71"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="122"/>
+      <c r="A19" s="123"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="150"/>
-      <c r="D19" s="151"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="153"/>
+      <c r="C19" s="156"/>
+      <c r="D19" s="157"/>
+      <c r="E19" s="188"/>
+      <c r="F19" s="176"/>
       <c r="G19" s="50"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -4271,20 +4271,20 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="121">
+      <c r="A20" s="122">
         <v>9</v>
       </c>
       <c r="B20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="126"/>
-      <c r="E20" s="141" t="s">
+      <c r="D20" s="184"/>
+      <c r="E20" s="185" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="143"/>
+      <c r="F20" s="175"/>
       <c r="G20" s="35"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -4347,14 +4347,14 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="122"/>
+      <c r="A21" s="123"/>
       <c r="B21" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="139"/>
-      <c r="D21" s="140"/>
-      <c r="E21" s="142"/>
-      <c r="F21" s="144"/>
+      <c r="C21" s="130"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="186"/>
+      <c r="F21" s="127"/>
       <c r="G21" s="47"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -4398,10 +4398,10 @@
       <c r="AU21" s="13"/>
       <c r="AV21" s="19"/>
       <c r="AW21" s="19"/>
-      <c r="AX21" s="201"/>
-      <c r="AY21" s="201"/>
-      <c r="AZ21" s="201"/>
-      <c r="BA21" s="201"/>
+      <c r="AX21" s="121"/>
+      <c r="AY21" s="121"/>
+      <c r="AZ21" s="121"/>
+      <c r="BA21" s="121"/>
       <c r="BB21" s="13"/>
       <c r="BC21" s="19"/>
       <c r="BD21" s="57"/>
@@ -4417,18 +4417,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="121">
+      <c r="A22" s="122">
         <v>10</v>
       </c>
       <c r="B22" s="33"/>
-      <c r="C22" s="145" t="s">
+      <c r="C22" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="146"/>
-      <c r="E22" s="147" t="s">
+      <c r="D22" s="129"/>
+      <c r="E22" s="187" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="148"/>
+      <c r="F22" s="126"/>
       <c r="G22" s="47"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4491,12 +4491,12 @@
       <c r="BN22" s="74"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="122"/>
+      <c r="A23" s="123"/>
       <c r="B23" s="33"/>
-      <c r="C23" s="139"/>
-      <c r="D23" s="140"/>
-      <c r="E23" s="142"/>
-      <c r="F23" s="144"/>
+      <c r="C23" s="130"/>
+      <c r="D23" s="131"/>
+      <c r="E23" s="186"/>
+      <c r="F23" s="127"/>
       <c r="G23" s="47"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -4540,10 +4540,10 @@
       <c r="AU23" s="13"/>
       <c r="AV23" s="19"/>
       <c r="AW23" s="19"/>
-      <c r="AX23" s="201"/>
-      <c r="AY23" s="201"/>
-      <c r="AZ23" s="201"/>
-      <c r="BA23" s="201"/>
+      <c r="AX23" s="121"/>
+      <c r="AY23" s="121"/>
+      <c r="AZ23" s="121"/>
+      <c r="BA23" s="121"/>
       <c r="BB23" s="13"/>
       <c r="BC23" s="19"/>
       <c r="BD23" s="57"/>
@@ -4559,18 +4559,18 @@
       <c r="BN23" s="74"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="121">
+      <c r="A24" s="122">
         <v>11</v>
       </c>
       <c r="B24" s="33"/>
-      <c r="C24" s="145" t="s">
+      <c r="C24" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="146"/>
-      <c r="E24" s="156" t="s">
+      <c r="D24" s="129"/>
+      <c r="E24" s="124" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="148"/>
+      <c r="F24" s="126"/>
       <c r="G24" s="48"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -4633,12 +4633,12 @@
       <c r="BN24" s="71"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="122"/>
+      <c r="A25" s="123"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="140"/>
-      <c r="E25" s="167"/>
-      <c r="F25" s="144"/>
+      <c r="C25" s="130"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="127"/>
       <c r="G25" s="48"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
@@ -4701,18 +4701,18 @@
       <c r="BN25" s="71"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="121">
+      <c r="A26" s="122">
         <v>12</v>
       </c>
       <c r="B26" s="33"/>
-      <c r="C26" s="145" t="s">
+      <c r="C26" s="128" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="146"/>
-      <c r="E26" s="156" t="s">
+      <c r="D26" s="129"/>
+      <c r="E26" s="124" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="148"/>
+      <c r="F26" s="126"/>
       <c r="G26" s="48"/>
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
@@ -4775,12 +4775,12 @@
       <c r="BN26" s="71"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="122"/>
+      <c r="A27" s="123"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="139"/>
-      <c r="D27" s="140"/>
-      <c r="E27" s="167"/>
-      <c r="F27" s="144"/>
+      <c r="C27" s="130"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="125"/>
+      <c r="F27" s="127"/>
       <c r="G27" s="48"/>
       <c r="H27" s="24"/>
       <c r="I27" s="24"/>
@@ -4843,20 +4843,20 @@
       <c r="BN27" s="71"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="121">
+      <c r="A28" s="122">
         <v>13</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="133" t="s">
+      <c r="C28" s="189" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="134"/>
-      <c r="E28" s="129" t="s">
+      <c r="D28" s="190"/>
+      <c r="E28" s="193" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="131"/>
+      <c r="F28" s="195"/>
       <c r="G28" s="35"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -4919,12 +4919,12 @@
       <c r="BN28" s="98"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="122"/>
+      <c r="A29" s="123"/>
       <c r="B29" s="31"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="136"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="138"/>
+      <c r="C29" s="191"/>
+      <c r="D29" s="192"/>
+      <c r="E29" s="194"/>
+      <c r="F29" s="161"/>
       <c r="G29" s="47"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -4987,20 +4987,20 @@
       <c r="BN29" s="94"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="121">
+      <c r="A30" s="122">
         <v>14</v>
       </c>
-      <c r="B30" s="123" t="s">
+      <c r="B30" s="196" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="125" t="s">
+      <c r="C30" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="126"/>
-      <c r="E30" s="129" t="s">
+      <c r="D30" s="184"/>
+      <c r="E30" s="193" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="131"/>
+      <c r="F30" s="195"/>
       <c r="G30" s="35"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
@@ -5063,12 +5063,12 @@
       <c r="BN30" s="98"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1" thickBot="1">
-      <c r="A31" s="122"/>
-      <c r="B31" s="124"/>
-      <c r="C31" s="127"/>
-      <c r="D31" s="128"/>
-      <c r="E31" s="130"/>
-      <c r="F31" s="132"/>
+      <c r="A31" s="123"/>
+      <c r="B31" s="197"/>
+      <c r="C31" s="198"/>
+      <c r="D31" s="199"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="201"/>
       <c r="G31" s="36"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -5154,49 +5154,11 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="C28:D29"/>
     <mergeCell ref="E28:E29"/>
@@ -5213,11 +5175,49 @@
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="C24:D25"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:E9"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/01_要件定義/03_WBS.xlsx
+++ b/01_要件定義/03_WBS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\01_要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB7CD0C-7FEA-4929-963E-63E2963069DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF19AF0-1AAD-4BDC-95B8-AB87D7C692F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="全体スケジュール" sheetId="13" r:id="rId1"/>
@@ -1435,7 +1435,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1798,29 +1798,128 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1891,15 +1990,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1909,9 +1999,6 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -1945,92 +2032,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2580,108 +2583,108 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BN35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="9.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="10.5"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.6640625" style="3" customWidth="1"/>
-    <col min="7" max="30" width="3.109375" style="3" customWidth="1"/>
-    <col min="31" max="66" width="3.109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.625" style="3" customWidth="1"/>
+    <col min="7" max="30" width="3.125" style="3" customWidth="1"/>
+    <col min="31" max="66" width="3.125" style="1" customWidth="1"/>
     <col min="67" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="135" t="s">
+      <c r="A1" s="168" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="138" t="s">
+      <c r="B1" s="171" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="141" t="s">
+      <c r="C1" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="142"/>
-      <c r="E1" s="147" t="s">
+      <c r="D1" s="175"/>
+      <c r="E1" s="180" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="150" t="s">
+      <c r="F1" s="183" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="132">
+      <c r="G1" s="165">
         <v>45536</v>
       </c>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="133"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="133"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="133"/>
-      <c r="AA1" s="133"/>
-      <c r="AB1" s="133"/>
-      <c r="AC1" s="133"/>
-      <c r="AD1" s="133"/>
-      <c r="AE1" s="133"/>
-      <c r="AF1" s="133"/>
-      <c r="AG1" s="133"/>
-      <c r="AH1" s="133"/>
-      <c r="AI1" s="133"/>
-      <c r="AJ1" s="134"/>
-      <c r="AK1" s="132">
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="166"/>
+      <c r="Q1" s="166"/>
+      <c r="R1" s="166"/>
+      <c r="S1" s="166"/>
+      <c r="T1" s="166"/>
+      <c r="U1" s="166"/>
+      <c r="V1" s="166"/>
+      <c r="W1" s="166"/>
+      <c r="X1" s="166"/>
+      <c r="Y1" s="166"/>
+      <c r="Z1" s="166"/>
+      <c r="AA1" s="166"/>
+      <c r="AB1" s="166"/>
+      <c r="AC1" s="166"/>
+      <c r="AD1" s="166"/>
+      <c r="AE1" s="166"/>
+      <c r="AF1" s="166"/>
+      <c r="AG1" s="166"/>
+      <c r="AH1" s="166"/>
+      <c r="AI1" s="166"/>
+      <c r="AJ1" s="167"/>
+      <c r="AK1" s="165">
         <v>45566</v>
       </c>
-      <c r="AL1" s="133"/>
-      <c r="AM1" s="133"/>
-      <c r="AN1" s="133"/>
-      <c r="AO1" s="133"/>
-      <c r="AP1" s="133"/>
-      <c r="AQ1" s="133"/>
-      <c r="AR1" s="133"/>
-      <c r="AS1" s="133"/>
-      <c r="AT1" s="133"/>
-      <c r="AU1" s="133"/>
-      <c r="AV1" s="133"/>
-      <c r="AW1" s="133"/>
-      <c r="AX1" s="133"/>
-      <c r="AY1" s="133"/>
-      <c r="AZ1" s="133"/>
-      <c r="BA1" s="133"/>
-      <c r="BB1" s="133"/>
-      <c r="BC1" s="133"/>
-      <c r="BD1" s="133"/>
-      <c r="BE1" s="133"/>
-      <c r="BF1" s="133"/>
-      <c r="BG1" s="133"/>
-      <c r="BH1" s="133"/>
-      <c r="BI1" s="133"/>
-      <c r="BJ1" s="133"/>
-      <c r="BK1" s="133"/>
-      <c r="BL1" s="133"/>
-      <c r="BM1" s="133"/>
-      <c r="BN1" s="134"/>
+      <c r="AL1" s="166"/>
+      <c r="AM1" s="166"/>
+      <c r="AN1" s="166"/>
+      <c r="AO1" s="166"/>
+      <c r="AP1" s="166"/>
+      <c r="AQ1" s="166"/>
+      <c r="AR1" s="166"/>
+      <c r="AS1" s="166"/>
+      <c r="AT1" s="166"/>
+      <c r="AU1" s="166"/>
+      <c r="AV1" s="166"/>
+      <c r="AW1" s="166"/>
+      <c r="AX1" s="166"/>
+      <c r="AY1" s="166"/>
+      <c r="AZ1" s="166"/>
+      <c r="BA1" s="166"/>
+      <c r="BB1" s="166"/>
+      <c r="BC1" s="166"/>
+      <c r="BD1" s="166"/>
+      <c r="BE1" s="166"/>
+      <c r="BF1" s="166"/>
+      <c r="BG1" s="166"/>
+      <c r="BH1" s="166"/>
+      <c r="BI1" s="166"/>
+      <c r="BJ1" s="166"/>
+      <c r="BK1" s="166"/>
+      <c r="BL1" s="166"/>
+      <c r="BM1" s="166"/>
+      <c r="BN1" s="167"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="148"/>
-      <c r="F2" s="151"/>
+      <c r="A2" s="169"/>
+      <c r="B2" s="172"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="177"/>
+      <c r="E2" s="181"/>
+      <c r="F2" s="184"/>
       <c r="G2" s="43">
         <v>45537</v>
       </c>
@@ -2923,12 +2926,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="137"/>
-      <c r="B3" s="140"/>
-      <c r="C3" s="145"/>
-      <c r="D3" s="146"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="152"/>
+      <c r="A3" s="170"/>
+      <c r="B3" s="173"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="182"/>
+      <c r="F3" s="185"/>
       <c r="G3" s="45" t="s">
         <v>14</v>
       </c>
@@ -3111,20 +3114,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="162">
+      <c r="A4" s="191">
         <v>1</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="163" t="s">
+      <c r="C4" s="192" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="164"/>
-      <c r="E4" s="165" t="s">
+      <c r="D4" s="193"/>
+      <c r="E4" s="194" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="167" t="s">
+      <c r="F4" s="196" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="89"/>
@@ -3189,12 +3192,12 @@
       <c r="BN4" s="65"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="154"/>
+      <c r="A5" s="187"/>
       <c r="B5" s="31"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="166"/>
-      <c r="F5" s="168"/>
+      <c r="C5" s="140"/>
+      <c r="D5" s="141"/>
+      <c r="E5" s="195"/>
+      <c r="F5" s="197"/>
       <c r="G5" s="90"/>
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
@@ -3257,18 +3260,18 @@
       <c r="BN5" s="66"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="153">
+      <c r="A6" s="186">
         <v>2</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="155" t="s">
+      <c r="C6" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="129"/>
-      <c r="E6" s="158" t="s">
+      <c r="D6" s="147"/>
+      <c r="E6" s="188" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="160" t="s">
+      <c r="F6" s="190" t="s">
         <v>37</v>
       </c>
       <c r="G6" s="47"/>
@@ -3333,12 +3336,12 @@
       <c r="BN6" s="67"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="154"/>
+      <c r="A7" s="187"/>
       <c r="B7" s="31"/>
-      <c r="C7" s="156"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="161"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="189"/>
+      <c r="F7" s="139"/>
       <c r="G7" s="48"/>
       <c r="H7" s="101"/>
       <c r="I7" s="58"/>
@@ -3407,14 +3410,14 @@
       <c r="B8" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="169" t="s">
+      <c r="C8" s="198" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="170"/>
-      <c r="E8" s="173" t="s">
+      <c r="D8" s="199"/>
+      <c r="E8" s="164" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="175" t="s">
+      <c r="F8" s="144" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="35"/>
@@ -3481,10 +3484,10 @@
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
       <c r="A9" s="123"/>
       <c r="B9" s="34"/>
-      <c r="C9" s="171"/>
-      <c r="D9" s="172"/>
-      <c r="E9" s="174"/>
-      <c r="F9" s="176"/>
+      <c r="C9" s="200"/>
+      <c r="D9" s="201"/>
+      <c r="E9" s="159"/>
+      <c r="F9" s="156"/>
       <c r="G9" s="49"/>
       <c r="H9" s="60"/>
       <c r="I9" s="60"/>
@@ -3553,14 +3556,14 @@
       <c r="B10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="177" t="s">
+      <c r="C10" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="178"/>
-      <c r="E10" s="173" t="s">
+      <c r="D10" s="161"/>
+      <c r="E10" s="164" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="175" t="s">
+      <c r="F10" s="144" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="46"/>
@@ -3627,10 +3630,10 @@
     <row r="11" spans="1:66" ht="12" customHeight="1">
       <c r="A11" s="123"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="179"/>
-      <c r="D11" s="180"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="127"/>
+      <c r="C11" s="162"/>
+      <c r="D11" s="163"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="145"/>
       <c r="G11" s="46"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
@@ -3697,14 +3700,14 @@
         <v>5</v>
       </c>
       <c r="B12" s="33"/>
-      <c r="C12" s="155" t="s">
+      <c r="C12" s="152" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="129"/>
-      <c r="E12" s="124" t="s">
+      <c r="D12" s="147"/>
+      <c r="E12" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="126" t="s">
+      <c r="F12" s="149" t="s">
         <v>39</v>
       </c>
       <c r="G12" s="47"/>
@@ -3771,10 +3774,10 @@
     <row r="13" spans="1:66" ht="12" customHeight="1">
       <c r="A13" s="123"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="181"/>
-      <c r="D13" s="182"/>
-      <c r="E13" s="174"/>
-      <c r="F13" s="176"/>
+      <c r="C13" s="157"/>
+      <c r="D13" s="158"/>
+      <c r="E13" s="159"/>
+      <c r="F13" s="156"/>
       <c r="G13" s="48"/>
       <c r="H13" s="58"/>
       <c r="I13" s="58"/>
@@ -3843,14 +3846,14 @@
       <c r="B14" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="183" t="s">
+      <c r="C14" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="184"/>
-      <c r="E14" s="185" t="s">
+      <c r="D14" s="127"/>
+      <c r="E14" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="175" t="s">
+      <c r="F14" s="144" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="35"/>
@@ -3917,10 +3920,10 @@
     <row r="15" spans="1:66" ht="12" customHeight="1">
       <c r="A15" s="123"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="130"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="186"/>
-      <c r="F15" s="127"/>
+      <c r="C15" s="140"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="145"/>
       <c r="G15" s="48"/>
       <c r="H15" s="58"/>
       <c r="I15" s="58"/>
@@ -3987,14 +3990,14 @@
         <v>7</v>
       </c>
       <c r="B16" s="33"/>
-      <c r="C16" s="155" t="s">
+      <c r="C16" s="152" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="129"/>
-      <c r="E16" s="187" t="s">
+      <c r="D16" s="147"/>
+      <c r="E16" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="126" t="s">
+      <c r="F16" s="149" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="47"/>
@@ -4061,10 +4064,10 @@
     <row r="17" spans="1:66" ht="12" customHeight="1">
       <c r="A17" s="123"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="131"/>
-      <c r="E17" s="186"/>
-      <c r="F17" s="127"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="145"/>
       <c r="G17" s="48"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -4131,14 +4134,14 @@
         <v>8</v>
       </c>
       <c r="B18" s="33"/>
-      <c r="C18" s="155" t="s">
+      <c r="C18" s="152" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="129"/>
-      <c r="E18" s="187" t="s">
+      <c r="D18" s="147"/>
+      <c r="E18" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="126" t="s">
+      <c r="F18" s="149" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="48"/>
@@ -4205,10 +4208,10 @@
     <row r="19" spans="1:66" ht="12" customHeight="1">
       <c r="A19" s="123"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="156"/>
-      <c r="D19" s="157"/>
-      <c r="E19" s="188"/>
-      <c r="F19" s="176"/>
+      <c r="C19" s="153"/>
+      <c r="D19" s="154"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="156"/>
       <c r="G19" s="50"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -4277,14 +4280,14 @@
       <c r="B20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="183" t="s">
+      <c r="C20" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="184"/>
-      <c r="E20" s="185" t="s">
+      <c r="D20" s="127"/>
+      <c r="E20" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="175"/>
+      <c r="F20" s="144"/>
       <c r="G20" s="35"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -4351,10 +4354,10 @@
       <c r="B21" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="130"/>
-      <c r="D21" s="131"/>
-      <c r="E21" s="186"/>
-      <c r="F21" s="127"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="145"/>
       <c r="G21" s="47"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -4421,14 +4424,14 @@
         <v>10</v>
       </c>
       <c r="B22" s="33"/>
-      <c r="C22" s="128" t="s">
+      <c r="C22" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="129"/>
-      <c r="E22" s="187" t="s">
+      <c r="D22" s="147"/>
+      <c r="E22" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="126"/>
+      <c r="F22" s="149"/>
       <c r="G22" s="47"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4493,10 +4496,10 @@
     <row r="23" spans="1:66" ht="12" customHeight="1">
       <c r="A23" s="123"/>
       <c r="B23" s="33"/>
-      <c r="C23" s="130"/>
-      <c r="D23" s="131"/>
-      <c r="E23" s="186"/>
-      <c r="F23" s="127"/>
+      <c r="C23" s="140"/>
+      <c r="D23" s="141"/>
+      <c r="E23" s="143"/>
+      <c r="F23" s="145"/>
       <c r="G23" s="47"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -4563,14 +4566,14 @@
         <v>11</v>
       </c>
       <c r="B24" s="33"/>
-      <c r="C24" s="128" t="s">
+      <c r="C24" s="146" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="129"/>
-      <c r="E24" s="124" t="s">
+      <c r="D24" s="147"/>
+      <c r="E24" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="126"/>
+      <c r="F24" s="149"/>
       <c r="G24" s="48"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -4635,10 +4638,10 @@
     <row r="25" spans="1:66" ht="12" customHeight="1">
       <c r="A25" s="123"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="130"/>
-      <c r="D25" s="131"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="127"/>
+      <c r="C25" s="140"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="145"/>
       <c r="G25" s="48"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
@@ -4705,14 +4708,14 @@
         <v>12</v>
       </c>
       <c r="B26" s="33"/>
-      <c r="C26" s="128" t="s">
+      <c r="C26" s="146" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="129"/>
-      <c r="E26" s="124" t="s">
+      <c r="D26" s="147"/>
+      <c r="E26" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="126"/>
+      <c r="F26" s="149"/>
       <c r="G26" s="48"/>
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
@@ -4777,10 +4780,10 @@
     <row r="27" spans="1:66" ht="12" customHeight="1">
       <c r="A27" s="123"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="125"/>
-      <c r="F27" s="127"/>
+      <c r="C27" s="140"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="151"/>
+      <c r="F27" s="145"/>
       <c r="G27" s="48"/>
       <c r="H27" s="24"/>
       <c r="I27" s="24"/>
@@ -4849,14 +4852,14 @@
       <c r="B28" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="189" t="s">
+      <c r="C28" s="134" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="190"/>
-      <c r="E28" s="193" t="s">
+      <c r="D28" s="135"/>
+      <c r="E28" s="130" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="195"/>
+      <c r="F28" s="132"/>
       <c r="G28" s="35"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -4913,7 +4916,7 @@
       <c r="BH28" s="91"/>
       <c r="BI28" s="15"/>
       <c r="BJ28" s="21"/>
-      <c r="BK28" s="91"/>
+      <c r="BK28" s="106"/>
       <c r="BL28" s="91"/>
       <c r="BM28" s="91"/>
       <c r="BN28" s="98"/>
@@ -4921,10 +4924,10 @@
     <row r="29" spans="1:66" ht="12" customHeight="1">
       <c r="A29" s="123"/>
       <c r="B29" s="31"/>
-      <c r="C29" s="191"/>
-      <c r="D29" s="192"/>
-      <c r="E29" s="194"/>
-      <c r="F29" s="161"/>
+      <c r="C29" s="136"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="139"/>
       <c r="G29" s="47"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -4974,11 +4977,11 @@
       <c r="BA29" s="57"/>
       <c r="BB29" s="13"/>
       <c r="BC29" s="19"/>
-      <c r="BD29" s="57"/>
-      <c r="BE29" s="57"/>
-      <c r="BF29" s="57"/>
-      <c r="BG29" s="57"/>
-      <c r="BH29" s="57"/>
+      <c r="BD29" s="121"/>
+      <c r="BE29" s="121"/>
+      <c r="BF29" s="121"/>
+      <c r="BG29" s="121"/>
+      <c r="BH29" s="121"/>
       <c r="BI29" s="13"/>
       <c r="BJ29" s="19"/>
       <c r="BK29" s="92"/>
@@ -4990,17 +4993,17 @@
       <c r="A30" s="122">
         <v>14</v>
       </c>
-      <c r="B30" s="196" t="s">
+      <c r="B30" s="124" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="183" t="s">
+      <c r="C30" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="184"/>
-      <c r="E30" s="193" t="s">
+      <c r="D30" s="127"/>
+      <c r="E30" s="130" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="195"/>
+      <c r="F30" s="132"/>
       <c r="G30" s="35"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
@@ -5057,18 +5060,18 @@
       <c r="BH30" s="37"/>
       <c r="BI30" s="15"/>
       <c r="BJ30" s="21"/>
-      <c r="BK30" s="91"/>
+      <c r="BK30" s="106"/>
       <c r="BL30" s="91"/>
       <c r="BM30" s="91"/>
       <c r="BN30" s="98"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1" thickBot="1">
       <c r="A31" s="123"/>
-      <c r="B31" s="197"/>
-      <c r="C31" s="198"/>
-      <c r="D31" s="199"/>
-      <c r="E31" s="200"/>
-      <c r="F31" s="201"/>
+      <c r="B31" s="125"/>
+      <c r="C31" s="128"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="133"/>
       <c r="G31" s="36"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -5122,7 +5125,7 @@
       <c r="BE31" s="63"/>
       <c r="BF31" s="63"/>
       <c r="BG31" s="63"/>
-      <c r="BH31" s="63"/>
+      <c r="BH31" s="202"/>
       <c r="BI31" s="14"/>
       <c r="BJ31" s="20"/>
       <c r="BK31" s="99"/>
@@ -5154,11 +5157,49 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="C26:D27"/>
+    <mergeCell ref="G1:AJ1"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="C28:D29"/>
     <mergeCell ref="E28:E29"/>
@@ -5175,49 +5216,11 @@
     <mergeCell ref="E26:E27"/>
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="C24:D25"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="C26:D27"/>
-    <mergeCell ref="G1:AJ1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>

--- a/01_要件定義/03_WBS.xlsx
+++ b/01_要件定義/03_WBS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\01_要件定義\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF19AF0-1AAD-4BDC-95B8-AB87D7C692F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F44A6A4D-9FD8-4171-B0E6-675697DF659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1792,248 +1792,248 @@
     <xf numFmtId="49" fontId="2" fillId="9" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="5" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2597,94 +2597,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="171" t="s">
+      <c r="B1" s="161" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="174" t="s">
+      <c r="C1" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="175"/>
-      <c r="E1" s="180" t="s">
+      <c r="D1" s="165"/>
+      <c r="E1" s="170" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="183" t="s">
+      <c r="F1" s="173" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="165">
+      <c r="G1" s="133">
         <v>45536</v>
       </c>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
-      <c r="L1" s="166"/>
-      <c r="M1" s="166"/>
-      <c r="N1" s="166"/>
-      <c r="O1" s="166"/>
-      <c r="P1" s="166"/>
-      <c r="Q1" s="166"/>
-      <c r="R1" s="166"/>
-      <c r="S1" s="166"/>
-      <c r="T1" s="166"/>
-      <c r="U1" s="166"/>
-      <c r="V1" s="166"/>
-      <c r="W1" s="166"/>
-      <c r="X1" s="166"/>
-      <c r="Y1" s="166"/>
-      <c r="Z1" s="166"/>
-      <c r="AA1" s="166"/>
-      <c r="AB1" s="166"/>
-      <c r="AC1" s="166"/>
-      <c r="AD1" s="166"/>
-      <c r="AE1" s="166"/>
-      <c r="AF1" s="166"/>
-      <c r="AG1" s="166"/>
-      <c r="AH1" s="166"/>
-      <c r="AI1" s="166"/>
-      <c r="AJ1" s="167"/>
-      <c r="AK1" s="165">
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="134"/>
+      <c r="K1" s="134"/>
+      <c r="L1" s="134"/>
+      <c r="M1" s="134"/>
+      <c r="N1" s="134"/>
+      <c r="O1" s="134"/>
+      <c r="P1" s="134"/>
+      <c r="Q1" s="134"/>
+      <c r="R1" s="134"/>
+      <c r="S1" s="134"/>
+      <c r="T1" s="134"/>
+      <c r="U1" s="134"/>
+      <c r="V1" s="134"/>
+      <c r="W1" s="134"/>
+      <c r="X1" s="134"/>
+      <c r="Y1" s="134"/>
+      <c r="Z1" s="134"/>
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="134"/>
+      <c r="AD1" s="134"/>
+      <c r="AE1" s="134"/>
+      <c r="AF1" s="134"/>
+      <c r="AG1" s="134"/>
+      <c r="AH1" s="134"/>
+      <c r="AI1" s="134"/>
+      <c r="AJ1" s="135"/>
+      <c r="AK1" s="133">
         <v>45566</v>
       </c>
-      <c r="AL1" s="166"/>
-      <c r="AM1" s="166"/>
-      <c r="AN1" s="166"/>
-      <c r="AO1" s="166"/>
-      <c r="AP1" s="166"/>
-      <c r="AQ1" s="166"/>
-      <c r="AR1" s="166"/>
-      <c r="AS1" s="166"/>
-      <c r="AT1" s="166"/>
-      <c r="AU1" s="166"/>
-      <c r="AV1" s="166"/>
-      <c r="AW1" s="166"/>
-      <c r="AX1" s="166"/>
-      <c r="AY1" s="166"/>
-      <c r="AZ1" s="166"/>
-      <c r="BA1" s="166"/>
-      <c r="BB1" s="166"/>
-      <c r="BC1" s="166"/>
-      <c r="BD1" s="166"/>
-      <c r="BE1" s="166"/>
-      <c r="BF1" s="166"/>
-      <c r="BG1" s="166"/>
-      <c r="BH1" s="166"/>
-      <c r="BI1" s="166"/>
-      <c r="BJ1" s="166"/>
-      <c r="BK1" s="166"/>
-      <c r="BL1" s="166"/>
-      <c r="BM1" s="166"/>
-      <c r="BN1" s="167"/>
+      <c r="AL1" s="134"/>
+      <c r="AM1" s="134"/>
+      <c r="AN1" s="134"/>
+      <c r="AO1" s="134"/>
+      <c r="AP1" s="134"/>
+      <c r="AQ1" s="134"/>
+      <c r="AR1" s="134"/>
+      <c r="AS1" s="134"/>
+      <c r="AT1" s="134"/>
+      <c r="AU1" s="134"/>
+      <c r="AV1" s="134"/>
+      <c r="AW1" s="134"/>
+      <c r="AX1" s="134"/>
+      <c r="AY1" s="134"/>
+      <c r="AZ1" s="134"/>
+      <c r="BA1" s="134"/>
+      <c r="BB1" s="134"/>
+      <c r="BC1" s="134"/>
+      <c r="BD1" s="134"/>
+      <c r="BE1" s="134"/>
+      <c r="BF1" s="134"/>
+      <c r="BG1" s="134"/>
+      <c r="BH1" s="134"/>
+      <c r="BI1" s="134"/>
+      <c r="BJ1" s="134"/>
+      <c r="BK1" s="134"/>
+      <c r="BL1" s="134"/>
+      <c r="BM1" s="134"/>
+      <c r="BN1" s="135"/>
     </row>
     <row r="2" spans="1:66" ht="10.5" customHeight="1">
-      <c r="A2" s="169"/>
-      <c r="B2" s="172"/>
-      <c r="C2" s="176"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="181"/>
-      <c r="F2" s="184"/>
+      <c r="A2" s="159"/>
+      <c r="B2" s="162"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="174"/>
       <c r="G2" s="43">
         <v>45537</v>
       </c>
@@ -2926,12 +2926,12 @@
       </c>
     </row>
     <row r="3" spans="1:66" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1">
-      <c r="A3" s="170"/>
-      <c r="B3" s="173"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="185"/>
+      <c r="A3" s="160"/>
+      <c r="B3" s="163"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="175"/>
       <c r="G3" s="45" t="s">
         <v>14</v>
       </c>
@@ -3114,20 +3114,20 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A4" s="191">
+      <c r="A4" s="145">
         <v>1</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="C4" s="146" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="193"/>
-      <c r="E4" s="194" t="s">
+      <c r="D4" s="147"/>
+      <c r="E4" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="196" t="s">
+      <c r="F4" s="150" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="89"/>
@@ -3192,12 +3192,12 @@
       <c r="BN4" s="65"/>
     </row>
     <row r="5" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A5" s="187"/>
+      <c r="A5" s="137"/>
       <c r="B5" s="31"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="141"/>
-      <c r="E5" s="195"/>
-      <c r="F5" s="197"/>
+      <c r="C5" s="131"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="151"/>
       <c r="G5" s="90"/>
       <c r="H5" s="56"/>
       <c r="I5" s="56"/>
@@ -3260,18 +3260,18 @@
       <c r="BN5" s="66"/>
     </row>
     <row r="6" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A6" s="186">
+      <c r="A6" s="136">
         <v>2</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="152" t="s">
+      <c r="C6" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="147"/>
-      <c r="E6" s="188" t="s">
+      <c r="D6" s="130"/>
+      <c r="E6" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="190" t="s">
+      <c r="F6" s="143" t="s">
         <v>37</v>
       </c>
       <c r="G6" s="47"/>
@@ -3336,12 +3336,12 @@
       <c r="BN6" s="67"/>
     </row>
     <row r="7" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A7" s="187"/>
+      <c r="A7" s="137"/>
       <c r="B7" s="31"/>
-      <c r="C7" s="153"/>
-      <c r="D7" s="154"/>
-      <c r="E7" s="189"/>
-      <c r="F7" s="139"/>
+      <c r="C7" s="139"/>
+      <c r="D7" s="140"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="144"/>
       <c r="G7" s="48"/>
       <c r="H7" s="101"/>
       <c r="I7" s="58"/>
@@ -3404,20 +3404,20 @@
       <c r="BN7" s="68"/>
     </row>
     <row r="8" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A8" s="122">
+      <c r="A8" s="123">
         <v>3</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="198" t="s">
+      <c r="C8" s="152" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="199"/>
-      <c r="E8" s="164" t="s">
+      <c r="D8" s="153"/>
+      <c r="E8" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="144" t="s">
+      <c r="F8" s="176" t="s">
         <v>38</v>
       </c>
       <c r="G8" s="35"/>
@@ -3482,12 +3482,12 @@
       <c r="BN8" s="69"/>
     </row>
     <row r="9" spans="1:66" ht="13.5" customHeight="1">
-      <c r="A9" s="123"/>
+      <c r="A9" s="124"/>
       <c r="B9" s="34"/>
-      <c r="C9" s="200"/>
-      <c r="D9" s="201"/>
-      <c r="E9" s="159"/>
-      <c r="F9" s="156"/>
+      <c r="C9" s="154"/>
+      <c r="D9" s="155"/>
+      <c r="E9" s="157"/>
+      <c r="F9" s="177"/>
       <c r="G9" s="49"/>
       <c r="H9" s="60"/>
       <c r="I9" s="60"/>
@@ -3550,20 +3550,20 @@
       <c r="BN9" s="70"/>
     </row>
     <row r="10" spans="1:66" ht="12" customHeight="1">
-      <c r="A10" s="122">
+      <c r="A10" s="123">
         <v>4</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="160" t="s">
+      <c r="C10" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="161"/>
-      <c r="E10" s="164" t="s">
+      <c r="D10" s="179"/>
+      <c r="E10" s="156" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="144" t="s">
+      <c r="F10" s="176" t="s">
         <v>36</v>
       </c>
       <c r="G10" s="46"/>
@@ -3628,12 +3628,12 @@
       <c r="BN10" s="66"/>
     </row>
     <row r="11" spans="1:66" ht="12" customHeight="1">
-      <c r="A11" s="123"/>
+      <c r="A11" s="124"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="162"/>
-      <c r="D11" s="163"/>
-      <c r="E11" s="151"/>
-      <c r="F11" s="145"/>
+      <c r="C11" s="180"/>
+      <c r="D11" s="181"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="128"/>
       <c r="G11" s="46"/>
       <c r="H11" s="56"/>
       <c r="I11" s="56"/>
@@ -3696,18 +3696,18 @@
       <c r="BN11" s="66"/>
     </row>
     <row r="12" spans="1:66" ht="12" customHeight="1">
-      <c r="A12" s="122">
+      <c r="A12" s="123">
         <v>5</v>
       </c>
       <c r="B12" s="33"/>
-      <c r="C12" s="152" t="s">
+      <c r="C12" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="147"/>
-      <c r="E12" s="150" t="s">
+      <c r="D12" s="130"/>
+      <c r="E12" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="149" t="s">
+      <c r="F12" s="127" t="s">
         <v>39</v>
       </c>
       <c r="G12" s="47"/>
@@ -3772,12 +3772,12 @@
       <c r="BN12" s="67"/>
     </row>
     <row r="13" spans="1:66" ht="12" customHeight="1">
-      <c r="A13" s="123"/>
+      <c r="A13" s="124"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="157"/>
-      <c r="D13" s="158"/>
-      <c r="E13" s="159"/>
-      <c r="F13" s="156"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="157"/>
+      <c r="F13" s="177"/>
       <c r="G13" s="48"/>
       <c r="H13" s="58"/>
       <c r="I13" s="58"/>
@@ -3840,20 +3840,20 @@
       <c r="BN13" s="68"/>
     </row>
     <row r="14" spans="1:66" ht="12" customHeight="1">
-      <c r="A14" s="122">
+      <c r="A14" s="123">
         <v>6</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="126" t="s">
+      <c r="C14" s="184" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="142" t="s">
+      <c r="D14" s="185"/>
+      <c r="E14" s="186" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="144" t="s">
+      <c r="F14" s="176" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="35"/>
@@ -3918,12 +3918,12 @@
       <c r="BN14" s="69"/>
     </row>
     <row r="15" spans="1:66" ht="12" customHeight="1">
-      <c r="A15" s="123"/>
+      <c r="A15" s="124"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="140"/>
-      <c r="D15" s="141"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="145"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="187"/>
+      <c r="F15" s="128"/>
       <c r="G15" s="48"/>
       <c r="H15" s="58"/>
       <c r="I15" s="58"/>
@@ -3986,18 +3986,18 @@
       <c r="BN15" s="68"/>
     </row>
     <row r="16" spans="1:66" ht="12" customHeight="1">
-      <c r="A16" s="122">
+      <c r="A16" s="123">
         <v>7</v>
       </c>
       <c r="B16" s="33"/>
-      <c r="C16" s="152" t="s">
+      <c r="C16" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="147"/>
-      <c r="E16" s="148" t="s">
+      <c r="D16" s="130"/>
+      <c r="E16" s="188" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="149" t="s">
+      <c r="F16" s="127" t="s">
         <v>40</v>
       </c>
       <c r="G16" s="47"/>
@@ -4062,12 +4062,12 @@
       <c r="BN16" s="67"/>
     </row>
     <row r="17" spans="1:66" ht="12" customHeight="1">
-      <c r="A17" s="123"/>
+      <c r="A17" s="124"/>
       <c r="B17" s="33"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="141"/>
-      <c r="E17" s="143"/>
-      <c r="F17" s="145"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="187"/>
+      <c r="F17" s="128"/>
       <c r="G17" s="48"/>
       <c r="H17" s="24"/>
       <c r="I17" s="24"/>
@@ -4130,18 +4130,18 @@
       <c r="BN17" s="68"/>
     </row>
     <row r="18" spans="1:66" ht="12" customHeight="1">
-      <c r="A18" s="122">
+      <c r="A18" s="123">
         <v>8</v>
       </c>
       <c r="B18" s="33"/>
-      <c r="C18" s="152" t="s">
+      <c r="C18" s="138" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="147"/>
-      <c r="E18" s="148" t="s">
+      <c r="D18" s="130"/>
+      <c r="E18" s="188" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="149" t="s">
+      <c r="F18" s="127" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="48"/>
@@ -4206,12 +4206,12 @@
       <c r="BN18" s="71"/>
     </row>
     <row r="19" spans="1:66" ht="12" customHeight="1">
-      <c r="A19" s="123"/>
+      <c r="A19" s="124"/>
       <c r="B19" s="34"/>
-      <c r="C19" s="153"/>
-      <c r="D19" s="154"/>
-      <c r="E19" s="155"/>
-      <c r="F19" s="156"/>
+      <c r="C19" s="139"/>
+      <c r="D19" s="140"/>
+      <c r="E19" s="189"/>
+      <c r="F19" s="177"/>
       <c r="G19" s="50"/>
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
@@ -4274,20 +4274,20 @@
       <c r="BN19" s="72"/>
     </row>
     <row r="20" spans="1:66" ht="12" customHeight="1">
-      <c r="A20" s="122">
+      <c r="A20" s="123">
         <v>9</v>
       </c>
       <c r="B20" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="126" t="s">
+      <c r="C20" s="184" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="127"/>
-      <c r="E20" s="142" t="s">
+      <c r="D20" s="185"/>
+      <c r="E20" s="186" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="144"/>
+      <c r="F20" s="176"/>
       <c r="G20" s="35"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
@@ -4350,14 +4350,14 @@
       <c r="BN20" s="73"/>
     </row>
     <row r="21" spans="1:66" ht="12" customHeight="1">
-      <c r="A21" s="123"/>
+      <c r="A21" s="124"/>
       <c r="B21" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="140"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="143"/>
-      <c r="F21" s="145"/>
+      <c r="C21" s="131"/>
+      <c r="D21" s="132"/>
+      <c r="E21" s="187"/>
+      <c r="F21" s="128"/>
       <c r="G21" s="47"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -4420,18 +4420,18 @@
       <c r="BN21" s="74"/>
     </row>
     <row r="22" spans="1:66" ht="12" customHeight="1">
-      <c r="A22" s="122">
+      <c r="A22" s="123">
         <v>10</v>
       </c>
       <c r="B22" s="33"/>
-      <c r="C22" s="146" t="s">
+      <c r="C22" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="147"/>
-      <c r="E22" s="148" t="s">
+      <c r="D22" s="130"/>
+      <c r="E22" s="188" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="149"/>
+      <c r="F22" s="127"/>
       <c r="G22" s="47"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4494,12 +4494,12 @@
       <c r="BN22" s="74"/>
     </row>
     <row r="23" spans="1:66" ht="12" customHeight="1">
-      <c r="A23" s="123"/>
+      <c r="A23" s="124"/>
       <c r="B23" s="33"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="141"/>
-      <c r="E23" s="143"/>
-      <c r="F23" s="145"/>
+      <c r="C23" s="131"/>
+      <c r="D23" s="132"/>
+      <c r="E23" s="187"/>
+      <c r="F23" s="128"/>
       <c r="G23" s="47"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -4562,18 +4562,18 @@
       <c r="BN23" s="74"/>
     </row>
     <row r="24" spans="1:66" ht="12" customHeight="1">
-      <c r="A24" s="122">
+      <c r="A24" s="123">
         <v>11</v>
       </c>
       <c r="B24" s="33"/>
-      <c r="C24" s="146" t="s">
+      <c r="C24" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="147"/>
-      <c r="E24" s="150" t="s">
+      <c r="D24" s="130"/>
+      <c r="E24" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="149"/>
+      <c r="F24" s="127"/>
       <c r="G24" s="48"/>
       <c r="H24" s="24"/>
       <c r="I24" s="24"/>
@@ -4636,12 +4636,12 @@
       <c r="BN24" s="71"/>
     </row>
     <row r="25" spans="1:66" ht="12" customHeight="1">
-      <c r="A25" s="123"/>
+      <c r="A25" s="124"/>
       <c r="B25" s="33"/>
-      <c r="C25" s="140"/>
-      <c r="D25" s="141"/>
-      <c r="E25" s="151"/>
-      <c r="F25" s="145"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="128"/>
       <c r="G25" s="48"/>
       <c r="H25" s="24"/>
       <c r="I25" s="24"/>
@@ -4704,18 +4704,18 @@
       <c r="BN25" s="71"/>
     </row>
     <row r="26" spans="1:66" ht="12" customHeight="1">
-      <c r="A26" s="122">
+      <c r="A26" s="123">
         <v>12</v>
       </c>
       <c r="B26" s="33"/>
-      <c r="C26" s="146" t="s">
+      <c r="C26" s="129" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="147"/>
-      <c r="E26" s="150" t="s">
+      <c r="D26" s="130"/>
+      <c r="E26" s="125" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="149"/>
+      <c r="F26" s="127"/>
       <c r="G26" s="48"/>
       <c r="H26" s="24"/>
       <c r="I26" s="24"/>
@@ -4778,12 +4778,12 @@
       <c r="BN26" s="71"/>
     </row>
     <row r="27" spans="1:66" ht="12" customHeight="1">
-      <c r="A27" s="123"/>
+      <c r="A27" s="124"/>
       <c r="B27" s="33"/>
-      <c r="C27" s="140"/>
-      <c r="D27" s="141"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="145"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="132"/>
+      <c r="E27" s="126"/>
+      <c r="F27" s="128"/>
       <c r="G27" s="48"/>
       <c r="H27" s="24"/>
       <c r="I27" s="24"/>
@@ -4846,20 +4846,20 @@
       <c r="BN27" s="71"/>
     </row>
     <row r="28" spans="1:66" ht="12" customHeight="1">
-      <c r="A28" s="122">
+      <c r="A28" s="123">
         <v>13</v>
       </c>
       <c r="B28" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="134" t="s">
+      <c r="C28" s="190" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="135"/>
-      <c r="E28" s="130" t="s">
+      <c r="D28" s="191"/>
+      <c r="E28" s="194" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="132"/>
+      <c r="F28" s="196"/>
       <c r="G28" s="35"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
@@ -4922,12 +4922,12 @@
       <c r="BN28" s="98"/>
     </row>
     <row r="29" spans="1:66" ht="12" customHeight="1">
-      <c r="A29" s="123"/>
+      <c r="A29" s="124"/>
       <c r="B29" s="31"/>
-      <c r="C29" s="136"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="139"/>
+      <c r="C29" s="192"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="195"/>
+      <c r="F29" s="144"/>
       <c r="G29" s="47"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
@@ -4984,26 +4984,26 @@
       <c r="BH29" s="121"/>
       <c r="BI29" s="13"/>
       <c r="BJ29" s="19"/>
-      <c r="BK29" s="92"/>
+      <c r="BK29" s="121"/>
       <c r="BL29" s="92"/>
       <c r="BM29" s="92"/>
       <c r="BN29" s="94"/>
     </row>
     <row r="30" spans="1:66" ht="12" customHeight="1">
-      <c r="A30" s="122">
+      <c r="A30" s="123">
         <v>14</v>
       </c>
-      <c r="B30" s="124" t="s">
+      <c r="B30" s="197" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="126" t="s">
+      <c r="C30" s="184" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="130" t="s">
+      <c r="D30" s="185"/>
+      <c r="E30" s="194" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="132"/>
+      <c r="F30" s="196"/>
       <c r="G30" s="35"/>
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
@@ -5066,12 +5066,12 @@
       <c r="BN30" s="98"/>
     </row>
     <row r="31" spans="1:66" ht="12" customHeight="1" thickBot="1">
-      <c r="A31" s="123"/>
-      <c r="B31" s="125"/>
-      <c r="C31" s="128"/>
-      <c r="D31" s="129"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="133"/>
+      <c r="A31" s="124"/>
+      <c r="B31" s="198"/>
+      <c r="C31" s="199"/>
+      <c r="D31" s="200"/>
+      <c r="E31" s="201"/>
+      <c r="F31" s="202"/>
       <c r="G31" s="36"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -5125,10 +5125,10 @@
       <c r="BE31" s="63"/>
       <c r="BF31" s="63"/>
       <c r="BG31" s="63"/>
-      <c r="BH31" s="202"/>
+      <c r="BH31" s="122"/>
       <c r="BI31" s="14"/>
       <c r="BJ31" s="20"/>
-      <c r="BK31" s="99"/>
+      <c r="BK31" s="122"/>
       <c r="BL31" s="99"/>
       <c r="BM31" s="99"/>
       <c r="BN31" s="100"/>
@@ -5157,6 +5157,54 @@
     </row>
   </sheetData>
   <mergeCells count="64">
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="C18:D19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="AK1:BN1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="F24:F25"/>
@@ -5173,54 +5221,6 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C8:D9"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="AK1:BN1"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="C12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="C14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="C18:D19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="F28:F29"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="C20:D21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="C22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
   </mergeCells>
   <phoneticPr fontId="4"/>
   <printOptions gridLinesSet="0"/>
